--- a/data/sources/drafts/DL_DRAFT1_FEV2026.xlsx
+++ b/data/sources/drafts/DL_DRAFT1_FEV2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DRAFT 1 " sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planilha1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="DRAFT 1 " sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Planilha1" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -916,20 +916,22 @@
       <c r="N4" s="25" t="n">
         <v>1231.07</v>
       </c>
-      <c r="O4" s="25" t="n"/>
+      <c r="O4" s="25" t="n">
+        <v>19</v>
+      </c>
       <c r="P4" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
       <c r="Q4" s="25" t="n">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="R4" s="25" t="n">
+        <v>27</v>
+      </c>
+      <c r="S4" s="25" t="n">
         <v>1231.07</v>
-      </c>
-      <c r="S4" s="25" t="n">
-        <v>1365.07</v>
       </c>
       <c r="T4" s="25" t="inlineStr">
         <is>
@@ -1084,11 +1086,7 @@
         <v>996.3</v>
       </c>
       <c r="O5" s="25" t="n"/>
-      <c r="P5" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P5" s="25" t="n"/>
       <c r="Q5" s="25" t="n"/>
       <c r="R5" s="25" t="n"/>
       <c r="S5" s="25" t="n"/>
@@ -1253,13 +1251,13 @@
         </is>
       </c>
       <c r="Q6" s="25" t="n">
-        <v>9</v>
+        <v>249</v>
       </c>
       <c r="R6" s="25" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="S6" s="25" t="n">
-        <v>2888.73</v>
+        <v>3941.77</v>
       </c>
       <c r="T6" s="25" t="inlineStr">
         <is>
@@ -1418,11 +1416,7 @@
         <v>795.39</v>
       </c>
       <c r="O7" s="25" t="n"/>
-      <c r="P7" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P7" s="25" t="n"/>
       <c r="Q7" s="25" t="n"/>
       <c r="R7" s="25" t="n"/>
       <c r="S7" s="25" t="n"/>
@@ -1587,13 +1581,13 @@
         </is>
       </c>
       <c r="Q8" s="25" t="n">
-        <v>33</v>
+        <v>132</v>
       </c>
       <c r="R8" s="25" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S8" s="25" t="n">
-        <v>4375.950000000001</v>
+        <v>4375.95</v>
       </c>
       <c r="T8" s="25" t="inlineStr">
         <is>
@@ -1752,7 +1746,7 @@
         <v>667.59</v>
       </c>
       <c r="O9" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P9" s="25" t="inlineStr">
         <is>
@@ -1760,13 +1754,13 @@
         </is>
       </c>
       <c r="Q9" s="25" t="n">
-        <v>18</v>
+        <v>165</v>
       </c>
       <c r="R9" s="25" t="n">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="S9" s="25" t="n">
-        <v>2296.45</v>
+        <v>2964.04</v>
       </c>
       <c r="T9" s="25" t="inlineStr">
         <is>
@@ -1933,7 +1927,7 @@
         </is>
       </c>
       <c r="Q10" s="25" t="n">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="R10" s="25" t="n">
         <v>15</v>
@@ -2106,10 +2100,10 @@
         </is>
       </c>
       <c r="Q11" s="25" t="n">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="R11" s="25" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="S11" s="25" t="n">
         <v>1140.63</v>
@@ -2262,7 +2256,7 @@
         </is>
       </c>
       <c r="Q12" s="25" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="R12" s="25" t="n">
         <v>10</v>
@@ -2418,11 +2412,7 @@
         <v>1121.85</v>
       </c>
       <c r="O13" s="25" t="n"/>
-      <c r="P13" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P13" s="25" t="n"/>
       <c r="Q13" s="25" t="n"/>
       <c r="R13" s="25" t="n"/>
       <c r="S13" s="25" t="n"/>
@@ -2574,7 +2564,7 @@
         <v>832.79</v>
       </c>
       <c r="O14" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P14" s="25" t="inlineStr">
         <is>
@@ -2582,13 +2572,13 @@
         </is>
       </c>
       <c r="Q14" s="25" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="R14" s="25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S14" s="25" t="n">
-        <v>1320.38</v>
+        <v>1492.98</v>
       </c>
       <c r="T14" s="25" t="inlineStr">
         <is>
@@ -2750,19 +2740,13 @@
         </is>
       </c>
       <c r="Q15" s="25" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="R15" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="S15" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="S15" s="25" t="n"/>
+      <c r="T15" s="25" t="n"/>
       <c r="U15" s="25" t="n">
         <v>0</v>
       </c>
@@ -2913,19 +2897,17 @@
       <c r="N16" s="25" t="n">
         <v>1491.36</v>
       </c>
-      <c r="O16" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="O16" s="25" t="n"/>
       <c r="P16" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
       <c r="Q16" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="R16" s="25" t="n">
         <v>1</v>
-      </c>
-      <c r="R16" s="25" t="n">
-        <v>0</v>
       </c>
       <c r="S16" s="25" t="n">
         <v>1093.04</v>
@@ -3086,11 +3068,7 @@
         <v>1919.52</v>
       </c>
       <c r="O17" s="25" t="n"/>
-      <c r="P17" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P17" s="25" t="n"/>
       <c r="Q17" s="25" t="n"/>
       <c r="R17" s="25" t="n"/>
       <c r="S17" s="25" t="n"/>
@@ -3238,13 +3216,13 @@
         </is>
       </c>
       <c r="Q18" s="25" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="R18" s="25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S18" s="25" t="n">
-        <v>1306.5</v>
+        <v>653.25</v>
       </c>
       <c r="T18" s="25" t="inlineStr">
         <is>
@@ -3398,11 +3376,7 @@
         <v>1552.1</v>
       </c>
       <c r="O19" s="25" t="n"/>
-      <c r="P19" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P19" s="25" t="n"/>
       <c r="Q19" s="25" t="n"/>
       <c r="R19" s="25" t="n"/>
       <c r="S19" s="25" t="n"/>
@@ -3554,11 +3528,7 @@
         <v>1405.05</v>
       </c>
       <c r="O20" s="25" t="n"/>
-      <c r="P20" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P20" s="25" t="n"/>
       <c r="Q20" s="25" t="n"/>
       <c r="R20" s="25" t="n"/>
       <c r="S20" s="25" t="n"/>
@@ -3722,13 +3692,13 @@
         </is>
       </c>
       <c r="Q21" s="25" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="R21" s="25" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="S21" s="25" t="n">
-        <v>3022.66</v>
+        <v>1511.33</v>
       </c>
       <c r="T21" s="25" t="inlineStr">
         <is>
@@ -3894,7 +3864,7 @@
         </is>
       </c>
       <c r="Q22" s="25" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="R22" s="25" t="n">
         <v>11</v>
@@ -4062,13 +4032,13 @@
         </is>
       </c>
       <c r="Q23" s="25" t="n">
-        <v>11</v>
+        <v>210</v>
       </c>
       <c r="R23" s="25" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S23" s="25" t="n">
-        <v>9851.84</v>
+        <v>7196.86</v>
       </c>
       <c r="T23" s="25" t="inlineStr">
         <is>
@@ -4222,7 +4192,7 @@
         <v>3110.35</v>
       </c>
       <c r="O24" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P24" s="25" t="inlineStr">
         <is>
@@ -4230,13 +4200,13 @@
         </is>
       </c>
       <c r="Q24" s="25" t="n">
-        <v>8</v>
+        <v>217</v>
       </c>
       <c r="R24" s="25" t="n">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="S24" s="25" t="n">
-        <v>7357.32</v>
+        <v>10467.67</v>
       </c>
       <c r="T24" s="25" t="inlineStr">
         <is>
@@ -4398,23 +4368,15 @@
       </c>
       <c r="P25" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="Q25" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="R25" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="R25" s="25" t="n"/>
+      <c r="S25" s="25" t="n"/>
+      <c r="T25" s="25" t="n"/>
       <c r="U25" s="25" t="n">
         <v>0</v>
       </c>
@@ -4562,11 +4524,7 @@
         <v>1383.4</v>
       </c>
       <c r="O26" s="25" t="n"/>
-      <c r="P26" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P26" s="25" t="n"/>
       <c r="Q26" s="25" t="n"/>
       <c r="R26" s="25" t="n"/>
       <c r="S26" s="25" t="n"/>
@@ -4726,10 +4684,10 @@
         </is>
       </c>
       <c r="Q27" s="25" t="n">
-        <v>82</v>
+        <v>615</v>
       </c>
       <c r="R27" s="25" t="n">
-        <v>291.79</v>
+        <v>114</v>
       </c>
       <c r="S27" s="25" t="n">
         <v>5722.39</v>
@@ -4886,11 +4844,7 @@
         <v>520</v>
       </c>
       <c r="O28" s="25" t="n"/>
-      <c r="P28" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P28" s="25" t="n"/>
       <c r="Q28" s="25" t="n"/>
       <c r="R28" s="25" t="n"/>
       <c r="S28" s="25" t="n"/>
@@ -5046,11 +5000,7 @@
         <v>1009.93</v>
       </c>
       <c r="O29" s="25" t="n"/>
-      <c r="P29" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P29" s="25" t="n"/>
       <c r="Q29" s="25" t="n"/>
       <c r="R29" s="25" t="n"/>
       <c r="S29" s="25" t="n"/>
@@ -5190,11 +5140,7 @@
         <v>2121.6</v>
       </c>
       <c r="O30" s="25" t="n"/>
-      <c r="P30" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P30" s="25" t="n"/>
       <c r="Q30" s="25" t="n"/>
       <c r="R30" s="25" t="n"/>
       <c r="S30" s="25" t="n"/>
@@ -5345,26 +5291,22 @@
       <c r="N31" s="25" t="n">
         <v>684.83</v>
       </c>
-      <c r="O31" s="25" t="n"/>
+      <c r="O31" s="25" t="n">
+        <v>31</v>
+      </c>
       <c r="P31" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
       <c r="Q31" s="25" t="n">
-        <v>31</v>
+        <v>171</v>
       </c>
       <c r="R31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" s="25" t="n">
-        <v>204</v>
-      </c>
-      <c r="T31" s="25" t="inlineStr">
-        <is>
-          <t>COMPRA B2B</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="S31" s="25" t="n"/>
+      <c r="T31" s="25" t="n"/>
       <c r="U31" s="25" t="n">
         <v>0</v>
       </c>
@@ -5520,10 +5462,10 @@
         </is>
       </c>
       <c r="Q32" s="25" t="n">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="R32" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S32" s="25" t="n">
         <v>685.71</v>
@@ -5679,20 +5621,22 @@
       <c r="N33" s="25" t="n">
         <v>767.7</v>
       </c>
-      <c r="O33" s="25" t="n"/>
+      <c r="O33" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="P33" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
       <c r="Q33" s="25" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="R33" s="25" t="n">
+        <v>17</v>
+      </c>
+      <c r="S33" s="25" t="n">
         <v>767.6799999999999</v>
-      </c>
-      <c r="S33" s="25" t="n">
-        <v>806.6799999999999</v>
       </c>
       <c r="T33" s="25" t="inlineStr">
         <is>
@@ -5854,7 +5798,7 @@
         </is>
       </c>
       <c r="Q34" s="25" t="n">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="R34" s="25" t="n">
         <v>15</v>
@@ -6017,20 +5961,22 @@
       <c r="N35" s="25" t="n">
         <v>698.62</v>
       </c>
-      <c r="O35" s="25" t="n"/>
+      <c r="O35" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="P35" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
       <c r="Q35" s="25" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="R35" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="S35" s="25" t="n">
         <v>698.62</v>
-      </c>
-      <c r="S35" s="25" t="n">
-        <v>749.62</v>
       </c>
       <c r="T35" s="25" t="inlineStr">
         <is>
@@ -6188,11 +6134,7 @@
         <v>2531.12</v>
       </c>
       <c r="O36" s="25" t="n"/>
-      <c r="P36" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P36" s="25" t="n"/>
       <c r="Q36" s="25" t="n"/>
       <c r="R36" s="25" t="n"/>
       <c r="S36" s="25" t="n"/>
@@ -6348,11 +6290,7 @@
         <v>669.61</v>
       </c>
       <c r="O37" s="25" t="n"/>
-      <c r="P37" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P37" s="25" t="n"/>
       <c r="Q37" s="25" t="n"/>
       <c r="R37" s="25" t="n"/>
       <c r="S37" s="25" t="n"/>
@@ -6512,10 +6450,10 @@
         </is>
       </c>
       <c r="Q38" s="25" t="n">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="R38" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S38" s="25" t="n">
         <v>361.23</v>
@@ -6676,14 +6614,14 @@
       </c>
       <c r="P39" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="Q39" s="25" t="n">
-        <v>29</v>
+        <v>171</v>
       </c>
       <c r="R39" s="25" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="S39" s="25" t="n">
         <v>697.77</v>
@@ -6839,19 +6777,17 @@
       <c r="N40" s="25" t="n">
         <v>934.5700000000001</v>
       </c>
-      <c r="O40" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="O40" s="25" t="n"/>
       <c r="P40" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
       <c r="Q40" s="25" t="n">
-        <v>19</v>
+        <v>270</v>
       </c>
       <c r="R40" s="25" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="S40" s="25" t="n">
         <v>2700.74</v>
@@ -7012,11 +6948,7 @@
         <v>1513.14</v>
       </c>
       <c r="O41" s="25" t="n"/>
-      <c r="P41" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P41" s="25" t="n"/>
       <c r="Q41" s="25" t="n"/>
       <c r="R41" s="25" t="n"/>
       <c r="S41" s="25" t="n"/>
@@ -7152,11 +7084,7 @@
         <v>17696.63</v>
       </c>
       <c r="O42" s="25" t="n"/>
-      <c r="P42" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P42" s="25" t="n"/>
       <c r="Q42" s="25" t="n"/>
       <c r="R42" s="25" t="n"/>
       <c r="S42" s="25" t="n"/>
@@ -7304,24 +7232,20 @@
       <c r="N43" s="25" t="n">
         <v>729.9400000000001</v>
       </c>
-      <c r="O43" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="O43" s="25" t="n"/>
+      <c r="P43" s="25" t="n"/>
       <c r="Q43" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" s="25" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="R43" s="25" t="n"/>
       <c r="S43" s="25" t="n">
         <v>924.6799999999999</v>
       </c>
-      <c r="T43" s="25" t="n"/>
+      <c r="T43" s="25" t="inlineStr">
+        <is>
+          <t>COMPRA B2B</t>
+        </is>
+      </c>
       <c r="U43" s="25" t="n">
         <v>0</v>
       </c>
@@ -7481,13 +7405,13 @@
         </is>
       </c>
       <c r="Q44" s="25" t="n">
-        <v>18</v>
+        <v>113</v>
       </c>
       <c r="R44" s="25" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="S44" s="25" t="n">
-        <v>10190.1</v>
+        <v>11985.62</v>
       </c>
       <c r="T44" s="25" t="inlineStr">
         <is>
@@ -7633,11 +7557,7 @@
         <v>696.9</v>
       </c>
       <c r="O45" s="25" t="n"/>
-      <c r="P45" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P45" s="25" t="n"/>
       <c r="Q45" s="25" t="n"/>
       <c r="R45" s="25" t="n"/>
       <c r="S45" s="25" t="n"/>
@@ -7801,13 +7721,13 @@
         </is>
       </c>
       <c r="Q46" s="25" t="n">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="R46" s="25" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S46" s="25" t="n">
-        <v>7316.29</v>
+        <v>8334.33</v>
       </c>
       <c r="T46" s="25" t="inlineStr">
         <is>
@@ -7973,13 +7893,13 @@
         </is>
       </c>
       <c r="Q47" s="25" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="R47" s="25" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="S47" s="25" t="n">
-        <v>5769.2</v>
+        <v>7268.39</v>
       </c>
       <c r="T47" s="25" t="inlineStr">
         <is>
@@ -8125,11 +8045,7 @@
         <v>1986.21</v>
       </c>
       <c r="O48" s="25" t="n"/>
-      <c r="P48" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P48" s="25" t="n"/>
       <c r="Q48" s="25" t="n"/>
       <c r="R48" s="25" t="n"/>
       <c r="S48" s="25" t="n"/>
@@ -8289,7 +8205,7 @@
         </is>
       </c>
       <c r="Q49" s="25" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="R49" s="25" t="n">
         <v>14</v>
@@ -8448,20 +8364,22 @@
       <c r="N50" s="25" t="n">
         <v>2831.66</v>
       </c>
-      <c r="O50" s="25" t="n"/>
+      <c r="O50" s="25" t="n">
+        <v>4</v>
+      </c>
       <c r="P50" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
       <c r="Q50" s="25" t="n">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="R50" s="25" t="n">
+        <v>30</v>
+      </c>
+      <c r="S50" s="25" t="n">
         <v>2831.66</v>
-      </c>
-      <c r="S50" s="25" t="n">
-        <v>2911.66</v>
       </c>
       <c r="T50" s="25" t="inlineStr">
         <is>
@@ -8611,11 +8529,7 @@
         <v>740.4299999999999</v>
       </c>
       <c r="O51" s="25" t="n"/>
-      <c r="P51" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P51" s="25" t="n"/>
       <c r="Q51" s="25" t="n"/>
       <c r="R51" s="25" t="n"/>
       <c r="S51" s="25" t="n"/>
@@ -8770,20 +8684,22 @@
       <c r="N52" s="25" t="n">
         <v>1699.51</v>
       </c>
-      <c r="O52" s="25" t="n"/>
+      <c r="O52" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="P52" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
       <c r="Q52" s="25" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="R52" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="S52" s="25" t="n">
         <v>1699.51</v>
-      </c>
-      <c r="S52" s="25" t="n">
-        <v>1735.51</v>
       </c>
       <c r="T52" s="25" t="inlineStr">
         <is>
@@ -8942,7 +8858,7 @@
         <v>1891.69</v>
       </c>
       <c r="O53" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P53" s="25" t="inlineStr">
         <is>
@@ -8950,17 +8866,17 @@
         </is>
       </c>
       <c r="Q53" s="25" t="n">
-        <v>4</v>
+        <v>139</v>
       </c>
       <c r="R53" s="25" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="S53" s="25" t="n">
-        <v>0</v>
+        <v>1891.69</v>
       </c>
       <c r="T53" s="25" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>COMPRA B2B</t>
         </is>
       </c>
       <c r="U53" s="25" t="n">
@@ -9094,11 +9010,7 @@
         <v>1122.91</v>
       </c>
       <c r="O54" s="25" t="n"/>
-      <c r="P54" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P54" s="25" t="n"/>
       <c r="Q54" s="25" t="n"/>
       <c r="R54" s="25" t="n"/>
       <c r="S54" s="25" t="n"/>
@@ -9258,10 +9170,10 @@
         </is>
       </c>
       <c r="Q55" s="25" t="n">
-        <v>17</v>
+        <v>157</v>
       </c>
       <c r="R55" s="25" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="S55" s="25" t="n">
         <v>2674.81</v>
@@ -9430,7 +9342,7 @@
         </is>
       </c>
       <c r="Q56" s="25" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="R56" s="25" t="n">
         <v>19</v>
@@ -9581,20 +9493,22 @@
       <c r="N57" s="25" t="n">
         <v>805.15</v>
       </c>
-      <c r="O57" s="25" t="n"/>
+      <c r="O57" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="P57" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
       <c r="Q57" s="25" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="R57" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="S57" s="25" t="n">
         <v>805.15</v>
-      </c>
-      <c r="S57" s="25" t="n">
-        <v>820.15</v>
       </c>
       <c r="T57" s="25" t="inlineStr">
         <is>
@@ -9748,7 +9662,7 @@
         <v>955.61</v>
       </c>
       <c r="O58" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P58" s="25" t="inlineStr">
         <is>
@@ -9756,17 +9670,17 @@
         </is>
       </c>
       <c r="Q58" s="25" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="R58" s="25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S58" s="25" t="n">
-        <v>0</v>
+        <v>955.61</v>
       </c>
       <c r="T58" s="25" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>COMPRA B2B</t>
         </is>
       </c>
       <c r="U58" s="25" t="n">
@@ -9912,11 +9826,7 @@
         <v>1690</v>
       </c>
       <c r="O59" s="25" t="n"/>
-      <c r="P59" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P59" s="25" t="n"/>
       <c r="Q59" s="25" t="n"/>
       <c r="R59" s="25" t="n"/>
       <c r="S59" s="25" t="n"/>
@@ -10076,10 +9986,10 @@
         </is>
       </c>
       <c r="Q60" s="25" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="R60" s="25" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S60" s="25" t="n">
         <v>2112.14</v>
@@ -10248,19 +10158,13 @@
         </is>
       </c>
       <c r="Q61" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R61" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="S61" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="S61" s="25" t="n"/>
+      <c r="T61" s="25" t="n"/>
       <c r="U61" s="25" t="n">
         <v>0</v>
       </c>
@@ -10416,7 +10320,7 @@
         </is>
       </c>
       <c r="Q62" s="25" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="R62" s="25" t="n">
         <v>23</v>
@@ -10572,11 +10476,7 @@
         <v>946.64</v>
       </c>
       <c r="O63" s="25" t="n"/>
-      <c r="P63" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P63" s="25" t="n"/>
       <c r="Q63" s="25" t="n"/>
       <c r="R63" s="25" t="n"/>
       <c r="S63" s="25" t="n"/>
@@ -10732,7 +10632,7 @@
         <v>612.47</v>
       </c>
       <c r="O64" s="25" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="P64" s="25" t="inlineStr">
         <is>
@@ -10740,13 +10640,13 @@
         </is>
       </c>
       <c r="Q64" s="25" t="n">
-        <v>27</v>
+        <v>301</v>
       </c>
       <c r="R64" s="25" t="n">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="S64" s="25" t="n">
-        <v>2035.83</v>
+        <v>2648.3</v>
       </c>
       <c r="T64" s="25" t="inlineStr">
         <is>
@@ -10908,10 +10808,10 @@
         </is>
       </c>
       <c r="Q65" s="25" t="n">
-        <v>5</v>
+        <v>150</v>
       </c>
       <c r="R65" s="25" t="n">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="S65" s="25" t="n">
         <v>5456.18</v>
@@ -11068,7 +10968,7 @@
         <v>776.61</v>
       </c>
       <c r="O66" s="25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P66" s="25" t="inlineStr">
         <is>
@@ -11076,13 +10976,13 @@
         </is>
       </c>
       <c r="Q66" s="25" t="n">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="R66" s="25" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="S66" s="25" t="n">
-        <v>1514.1</v>
+        <v>2290.71</v>
       </c>
       <c r="T66" s="25" t="inlineStr">
         <is>
@@ -11244,13 +11144,13 @@
         </is>
       </c>
       <c r="Q67" s="25" t="n">
-        <v>24</v>
+        <v>170</v>
       </c>
       <c r="R67" s="25" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="S67" s="25" t="n">
-        <v>2237.67</v>
+        <v>3456.44</v>
       </c>
       <c r="T67" s="25" t="inlineStr">
         <is>
@@ -11404,7 +11304,7 @@
         <v>880.47</v>
       </c>
       <c r="O68" s="25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P68" s="25" t="inlineStr">
         <is>
@@ -11412,10 +11312,10 @@
         </is>
       </c>
       <c r="Q68" s="25" t="n">
-        <v>14</v>
+        <v>204</v>
       </c>
       <c r="R68" s="25" t="n">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="S68" s="25" t="n">
         <v>3333.11</v>
@@ -11572,7 +11472,7 @@
         <v>1386.83</v>
       </c>
       <c r="O69" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P69" s="25" t="inlineStr">
         <is>
@@ -11580,10 +11480,10 @@
         </is>
       </c>
       <c r="Q69" s="25" t="n">
-        <v>22</v>
+        <v>292</v>
       </c>
       <c r="R69" s="25" t="n">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="S69" s="25" t="n">
         <v>4308.24</v>
@@ -11740,7 +11640,7 @@
         <v>259.86</v>
       </c>
       <c r="O70" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P70" s="25" t="inlineStr">
         <is>
@@ -11748,13 +11648,13 @@
         </is>
       </c>
       <c r="Q70" s="25" t="n">
-        <v>4</v>
+        <v>158</v>
       </c>
       <c r="R70" s="25" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="S70" s="25" t="n">
-        <v>568.6</v>
+        <v>819.9299999999999</v>
       </c>
       <c r="T70" s="25" t="inlineStr">
         <is>
@@ -11916,7 +11816,7 @@
         </is>
       </c>
       <c r="Q71" s="25" t="n">
-        <v>2</v>
+        <v>98</v>
       </c>
       <c r="R71" s="25" t="n">
         <v>17</v>
@@ -12084,10 +11984,10 @@
         </is>
       </c>
       <c r="Q72" s="25" t="n">
-        <v>10</v>
+        <v>238</v>
       </c>
       <c r="R72" s="25" t="n">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="S72" s="25" t="n">
         <v>2467</v>
@@ -12244,11 +12144,7 @@
         <v>1431.2</v>
       </c>
       <c r="O73" s="25" t="n"/>
-      <c r="P73" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P73" s="25" t="n"/>
       <c r="Q73" s="25" t="n"/>
       <c r="R73" s="25" t="n"/>
       <c r="S73" s="25" t="n"/>
@@ -12400,7 +12296,7 @@
         <v>3422.4</v>
       </c>
       <c r="O74" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P74" s="25" t="inlineStr">
         <is>
@@ -12408,7 +12304,7 @@
         </is>
       </c>
       <c r="Q74" s="25" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="R74" s="25" t="n">
         <v>1</v>
@@ -12572,13 +12468,13 @@
         </is>
       </c>
       <c r="Q75" s="25" t="n">
-        <v>7</v>
+        <v>76</v>
       </c>
       <c r="R75" s="25" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="S75" s="25" t="n">
-        <v>7500.76</v>
+        <v>3750.38</v>
       </c>
       <c r="T75" s="25" t="inlineStr">
         <is>
@@ -12728,11 +12624,7 @@
         <v>1118.86</v>
       </c>
       <c r="O76" s="25" t="n"/>
-      <c r="P76" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P76" s="25" t="n"/>
       <c r="Q76" s="25" t="n"/>
       <c r="R76" s="25" t="n"/>
       <c r="S76" s="25" t="n"/>
@@ -12892,19 +12784,13 @@
         </is>
       </c>
       <c r="Q77" s="25" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="R77" s="25" t="n">
         <v>26</v>
       </c>
-      <c r="S77" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T77" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="S77" s="25" t="n"/>
+      <c r="T77" s="25" t="n"/>
       <c r="U77" s="25" t="n">
         <v>0</v>
       </c>
@@ -13056,10 +12942,10 @@
         </is>
       </c>
       <c r="Q78" s="25" t="n">
-        <v>7</v>
+        <v>158</v>
       </c>
       <c r="R78" s="25" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="S78" s="25" t="n">
         <v>1102.1</v>
@@ -13216,11 +13102,7 @@
         <v>351.82</v>
       </c>
       <c r="O79" s="25" t="n"/>
-      <c r="P79" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P79" s="25" t="n"/>
       <c r="Q79" s="25" t="n"/>
       <c r="R79" s="25" t="n"/>
       <c r="S79" s="25" t="n"/>
@@ -13372,7 +13254,7 @@
         <v>403.98</v>
       </c>
       <c r="O80" s="25" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P80" s="25" t="inlineStr">
         <is>
@@ -13380,7 +13262,7 @@
         </is>
       </c>
       <c r="Q80" s="25" t="n">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="R80" s="25" t="n">
         <v>41</v>
@@ -13540,7 +13422,7 @@
         <v>966.75</v>
       </c>
       <c r="O81" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P81" s="25" t="inlineStr">
         <is>
@@ -13548,13 +13430,13 @@
         </is>
       </c>
       <c r="Q81" s="25" t="n">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="R81" s="25" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="S81" s="25" t="n">
-        <v>1670.94</v>
+        <v>2637.69</v>
       </c>
       <c r="T81" s="25" t="inlineStr">
         <is>
@@ -13718,17 +13600,9 @@
       <c r="Q82" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="R82" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S82" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T82" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="R82" s="25" t="n"/>
+      <c r="S82" s="25" t="n"/>
+      <c r="T82" s="25" t="n"/>
       <c r="U82" s="25" t="n">
         <v>0</v>
       </c>
@@ -13876,11 +13750,7 @@
         <v>269.5</v>
       </c>
       <c r="O83" s="25" t="n"/>
-      <c r="P83" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P83" s="25" t="n"/>
       <c r="Q83" s="25" t="n"/>
       <c r="R83" s="25" t="n"/>
       <c r="S83" s="25" t="n"/>
@@ -14035,20 +13905,22 @@
       <c r="N84" s="25" t="n">
         <v>1501.12</v>
       </c>
-      <c r="O84" s="25" t="n"/>
+      <c r="O84" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="P84" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
       <c r="Q84" s="25" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="R84" s="25" t="n">
+        <v>33</v>
+      </c>
+      <c r="S84" s="25" t="n">
         <v>1501.12</v>
-      </c>
-      <c r="S84" s="25" t="n">
-        <v>1566.12</v>
       </c>
       <c r="T84" s="25" t="inlineStr">
         <is>
@@ -14206,7 +14078,7 @@
         </is>
       </c>
       <c r="Q85" s="25" t="n">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="R85" s="25" t="n">
         <v>36</v>
@@ -14370,11 +14242,7 @@
         <v>1572.15</v>
       </c>
       <c r="O86" s="25" t="n"/>
-      <c r="P86" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P86" s="25" t="n"/>
       <c r="Q86" s="25" t="n"/>
       <c r="R86" s="25" t="n"/>
       <c r="S86" s="25" t="n"/>
@@ -14517,20 +14385,22 @@
       <c r="N87" s="25" t="n">
         <v>1562.74</v>
       </c>
-      <c r="O87" s="25" t="n"/>
+      <c r="O87" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="P87" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
       <c r="Q87" s="25" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="R87" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="S87" s="25" t="n">
         <v>1562.74</v>
-      </c>
-      <c r="S87" s="25" t="n">
-        <v>1580.74</v>
       </c>
       <c r="T87" s="25" t="inlineStr">
         <is>
@@ -14684,7 +14554,7 @@
         <v>2501.31</v>
       </c>
       <c r="O88" s="25" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P88" s="25" t="inlineStr">
         <is>
@@ -14692,10 +14562,10 @@
         </is>
       </c>
       <c r="Q88" s="25" t="n">
-        <v>6</v>
+        <v>161</v>
       </c>
       <c r="R88" s="25" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S88" s="25" t="n">
         <v>5910.57</v>
@@ -14860,10 +14730,10 @@
         </is>
       </c>
       <c r="Q89" s="25" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="R89" s="25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S89" s="25" t="n">
         <v>728.46</v>
@@ -15024,7 +14894,7 @@
         <v>677.3099999999999</v>
       </c>
       <c r="O90" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P90" s="25" t="inlineStr">
         <is>
@@ -15032,17 +14902,17 @@
         </is>
       </c>
       <c r="Q90" s="25" t="n">
-        <v>1</v>
+        <v>125</v>
       </c>
       <c r="R90" s="25" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="S90" s="25" t="n">
-        <v>0</v>
+        <v>677.3099999999999</v>
       </c>
       <c r="T90" s="25" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>COMPRA B2B</t>
         </is>
       </c>
       <c r="U90" s="25" t="n">
@@ -15188,7 +15058,7 @@
         </is>
       </c>
       <c r="Q91" s="25" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="R91" s="25" t="n">
         <v>1</v>
@@ -15348,11 +15218,7 @@
         <v>1040.88</v>
       </c>
       <c r="O92" s="25" t="n"/>
-      <c r="P92" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P92" s="25" t="n"/>
       <c r="Q92" s="25" t="n"/>
       <c r="R92" s="25" t="n"/>
       <c r="S92" s="25" t="n"/>
@@ -15504,11 +15370,7 @@
         <v>1274.24</v>
       </c>
       <c r="O93" s="25" t="n"/>
-      <c r="P93" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P93" s="25" t="n"/>
       <c r="Q93" s="25" t="n"/>
       <c r="R93" s="25" t="n"/>
       <c r="S93" s="25" t="n"/>
@@ -15660,11 +15522,7 @@
         <v>2479.64</v>
       </c>
       <c r="O94" s="25" t="n"/>
-      <c r="P94" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P94" s="25" t="n"/>
       <c r="Q94" s="25" t="n"/>
       <c r="R94" s="25" t="n"/>
       <c r="S94" s="25" t="n"/>
@@ -15816,11 +15674,7 @@
         <v>1494.46</v>
       </c>
       <c r="O95" s="25" t="n"/>
-      <c r="P95" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P95" s="25" t="n"/>
       <c r="Q95" s="25" t="n"/>
       <c r="R95" s="25" t="n"/>
       <c r="S95" s="25" t="n"/>
@@ -15972,11 +15826,7 @@
         <v>2102.98</v>
       </c>
       <c r="O96" s="25" t="n"/>
-      <c r="P96" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P96" s="25" t="n"/>
       <c r="Q96" s="25" t="n"/>
       <c r="R96" s="25" t="n"/>
       <c r="S96" s="25" t="n"/>
@@ -16128,11 +15978,7 @@
         <v>1992.13</v>
       </c>
       <c r="O97" s="25" t="n"/>
-      <c r="P97" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P97" s="25" t="n"/>
       <c r="Q97" s="25" t="n"/>
       <c r="R97" s="25" t="n"/>
       <c r="S97" s="25" t="n"/>
@@ -16292,10 +16138,10 @@
         </is>
       </c>
       <c r="Q98" s="25" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="R98" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S98" s="25" t="n">
         <v>3448</v>
@@ -16452,11 +16298,7 @@
         <v>689.63</v>
       </c>
       <c r="O99" s="25" t="n"/>
-      <c r="P99" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P99" s="25" t="n"/>
       <c r="Q99" s="25" t="n"/>
       <c r="R99" s="25" t="n"/>
       <c r="S99" s="25" t="n"/>
@@ -16604,11 +16446,7 @@
         <v>1217.88</v>
       </c>
       <c r="O100" s="25" t="n"/>
-      <c r="P100" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P100" s="25" t="n"/>
       <c r="Q100" s="25" t="n"/>
       <c r="R100" s="25" t="n"/>
       <c r="S100" s="25" t="n"/>
@@ -16763,26 +16601,22 @@
       <c r="N101" s="25" t="n">
         <v>1322.77</v>
       </c>
-      <c r="O101" s="25" t="n"/>
+      <c r="O101" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="P101" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
       <c r="Q101" s="25" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="R101" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S101" s="25" t="n">
-        <v>31</v>
-      </c>
-      <c r="T101" s="25" t="inlineStr">
-        <is>
-          <t>COMPRA B2B</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="S101" s="25" t="n"/>
+      <c r="T101" s="25" t="n"/>
       <c r="U101" s="25" t="n">
         <v>0</v>
       </c>
@@ -16930,7 +16764,7 @@
         <v>222.21</v>
       </c>
       <c r="O102" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P102" s="25" t="inlineStr">
         <is>
@@ -16938,17 +16772,17 @@
         </is>
       </c>
       <c r="Q102" s="25" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="R102" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S102" s="25" t="n">
-        <v>0</v>
+        <v>395.61</v>
       </c>
       <c r="T102" s="25" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>COMPRA B2B</t>
         </is>
       </c>
       <c r="U102" s="25" t="n">
@@ -17098,11 +16932,7 @@
         <v>16588.98</v>
       </c>
       <c r="O103" s="25" t="n"/>
-      <c r="P103" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P103" s="25" t="n"/>
       <c r="Q103" s="25" t="n"/>
       <c r="R103" s="25" t="n"/>
       <c r="S103" s="25" t="n"/>
@@ -17262,7 +17092,7 @@
         </is>
       </c>
       <c r="Q104" s="25" t="n">
-        <v>7</v>
+        <v>154</v>
       </c>
       <c r="R104" s="25" t="n">
         <v>73</v>
@@ -17422,11 +17252,7 @@
         <v>279</v>
       </c>
       <c r="O105" s="25" t="n"/>
-      <c r="P105" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P105" s="25" t="n"/>
       <c r="Q105" s="25" t="n"/>
       <c r="R105" s="25" t="n"/>
       <c r="S105" s="25" t="n"/>
@@ -17582,11 +17408,7 @@
         <v>1540.96</v>
       </c>
       <c r="O106" s="25" t="n"/>
-      <c r="P106" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P106" s="25" t="n"/>
       <c r="Q106" s="25" t="n"/>
       <c r="R106" s="25" t="n"/>
       <c r="S106" s="25" t="n"/>
@@ -17738,11 +17560,7 @@
         <v>2518.19</v>
       </c>
       <c r="O107" s="25" t="n"/>
-      <c r="P107" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P107" s="25" t="n"/>
       <c r="Q107" s="25" t="n"/>
       <c r="R107" s="25" t="n"/>
       <c r="S107" s="25" t="n"/>
@@ -17882,11 +17700,7 @@
         <v>2018.5</v>
       </c>
       <c r="O108" s="25" t="n"/>
-      <c r="P108" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P108" s="25" t="n"/>
       <c r="Q108" s="25" t="n"/>
       <c r="R108" s="25" t="n"/>
       <c r="S108" s="25" t="n"/>
@@ -18029,13 +17843,17 @@
       <c r="N109" s="25" t="n">
         <v>1126.29</v>
       </c>
-      <c r="O109" s="25" t="n"/>
+      <c r="O109" s="25" t="n">
+        <v>2</v>
+      </c>
       <c r="P109" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="Q109" s="25" t="n"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q109" s="25" t="n">
+        <v>2</v>
+      </c>
       <c r="R109" s="25" t="n"/>
       <c r="S109" s="25" t="n"/>
       <c r="T109" s="25" t="n"/>
@@ -18190,7 +18008,7 @@
         <v>427.41</v>
       </c>
       <c r="O110" s="25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P110" s="25" t="inlineStr">
         <is>
@@ -18198,17 +18016,17 @@
         </is>
       </c>
       <c r="Q110" s="25" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="R110" s="25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S110" s="25" t="n">
-        <v>0</v>
+        <v>924.0700000000001</v>
       </c>
       <c r="T110" s="25" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>COMPRA B2B</t>
         </is>
       </c>
       <c r="U110" s="25" t="n">
@@ -18362,11 +18180,7 @@
         <v>1159.21</v>
       </c>
       <c r="O111" s="25" t="n"/>
-      <c r="P111" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P111" s="25" t="n"/>
       <c r="Q111" s="25" t="n"/>
       <c r="R111" s="25" t="n"/>
       <c r="S111" s="25" t="n"/>
@@ -18518,11 +18332,7 @@
         <v>950.7</v>
       </c>
       <c r="O112" s="25" t="n"/>
-      <c r="P112" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P112" s="25" t="n"/>
       <c r="Q112" s="25" t="n"/>
       <c r="R112" s="25" t="n"/>
       <c r="S112" s="25" t="n"/>
@@ -18674,7 +18484,7 @@
         <v>2283.13</v>
       </c>
       <c r="O113" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P113" s="25" t="inlineStr">
         <is>
@@ -18682,13 +18492,13 @@
         </is>
       </c>
       <c r="Q113" s="25" t="n">
-        <v>23</v>
+        <v>274</v>
       </c>
       <c r="R113" s="25" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="S113" s="25" t="n">
-        <v>4657.27</v>
+        <v>6940.4</v>
       </c>
       <c r="T113" s="25" t="inlineStr">
         <is>
@@ -18855,13 +18665,13 @@
         </is>
       </c>
       <c r="Q114" s="25" t="n">
-        <v>8</v>
+        <v>107</v>
       </c>
       <c r="R114" s="25" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="S114" s="25" t="n">
-        <v>2380.62</v>
+        <v>1190.31</v>
       </c>
       <c r="T114" s="25" t="inlineStr">
         <is>
@@ -19023,13 +18833,13 @@
         </is>
       </c>
       <c r="Q115" s="25" t="n">
-        <v>26</v>
+        <v>141</v>
       </c>
       <c r="R115" s="25" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="S115" s="25" t="n">
-        <v>54146.29</v>
+        <v>51045.49</v>
       </c>
       <c r="T115" s="25" t="inlineStr">
         <is>
@@ -19183,11 +18993,7 @@
         <v>897.14</v>
       </c>
       <c r="O116" s="25" t="n"/>
-      <c r="P116" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P116" s="25" t="n"/>
       <c r="Q116" s="25" t="n"/>
       <c r="R116" s="25" t="n"/>
       <c r="S116" s="25" t="n"/>
@@ -19347,19 +19153,11 @@
         </is>
       </c>
       <c r="Q117" s="25" t="n">
-        <v>14</v>
-      </c>
-      <c r="R117" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S117" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T117" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="R117" s="25" t="n"/>
+      <c r="S117" s="25" t="n"/>
+      <c r="T117" s="25" t="n"/>
       <c r="U117" s="25" t="n">
         <v>0</v>
       </c>
@@ -19515,10 +19313,10 @@
         </is>
       </c>
       <c r="Q118" s="25" t="n">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="R118" s="25" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="S118" s="25" t="n">
         <v>3545.87</v>
@@ -19675,11 +19473,7 @@
         <v>650.02</v>
       </c>
       <c r="O119" s="25" t="n"/>
-      <c r="P119" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P119" s="25" t="n"/>
       <c r="Q119" s="25" t="n"/>
       <c r="R119" s="25" t="n"/>
       <c r="S119" s="25" t="n"/>
@@ -19835,11 +19629,7 @@
         <v>2098.89</v>
       </c>
       <c r="O120" s="25" t="n"/>
-      <c r="P120" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P120" s="25" t="n"/>
       <c r="Q120" s="25" t="n"/>
       <c r="R120" s="25" t="n"/>
       <c r="S120" s="25" t="n"/>
@@ -19991,11 +19781,7 @@
         <v>2378.6</v>
       </c>
       <c r="O121" s="25" t="n"/>
-      <c r="P121" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P121" s="25" t="n"/>
       <c r="Q121" s="25" t="n"/>
       <c r="R121" s="25" t="n"/>
       <c r="S121" s="25" t="n"/>
@@ -20135,11 +19921,7 @@
         <v>926.96</v>
       </c>
       <c r="O122" s="25" t="n"/>
-      <c r="P122" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P122" s="25" t="n"/>
       <c r="Q122" s="25" t="n"/>
       <c r="R122" s="25" t="n"/>
       <c r="S122" s="25" t="n"/>
@@ -20291,11 +20073,7 @@
         <v>997.5</v>
       </c>
       <c r="O123" s="25" t="n"/>
-      <c r="P123" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P123" s="25" t="n"/>
       <c r="Q123" s="25" t="n"/>
       <c r="R123" s="25" t="n"/>
       <c r="S123" s="25" t="n"/>
@@ -20451,25 +20229,11 @@
         <v>784.09</v>
       </c>
       <c r="O124" s="25" t="n"/>
-      <c r="P124" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="Q124" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="R124" s="25" t="n">
-        <v>1462.09</v>
-      </c>
-      <c r="S124" s="25" t="n">
-        <v>1642.09</v>
-      </c>
-      <c r="T124" s="25" t="inlineStr">
-        <is>
-          <t>COMPRA B2B</t>
-        </is>
-      </c>
+      <c r="P124" s="25" t="n"/>
+      <c r="Q124" s="25" t="n"/>
+      <c r="R124" s="25" t="n"/>
+      <c r="S124" s="25" t="n"/>
+      <c r="T124" s="25" t="n"/>
       <c r="U124" s="25" t="n">
         <v>0</v>
       </c>
@@ -20613,19 +20377,11 @@
         </is>
       </c>
       <c r="Q125" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R125" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S125" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T125" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="R125" s="25" t="n"/>
+      <c r="S125" s="25" t="n"/>
+      <c r="T125" s="25" t="n"/>
       <c r="U125" s="25" t="n">
         <v>0</v>
       </c>
@@ -20781,10 +20537,10 @@
         </is>
       </c>
       <c r="Q126" s="25" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="R126" s="25" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S126" s="25" t="n">
         <v>1110.39</v>
@@ -20937,10 +20693,10 @@
         </is>
       </c>
       <c r="Q127" s="25" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="R127" s="25" t="n">
-        <v>554.65</v>
+        <v>6</v>
       </c>
       <c r="S127" s="25" t="n">
         <v>728.92</v>
@@ -21093,7 +20849,7 @@
         </is>
       </c>
       <c r="Q128" s="25" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="R128" s="25" t="n">
         <v>10</v>
@@ -21240,19 +20996,17 @@
       <c r="N129" s="25" t="n">
         <v>1458.94</v>
       </c>
-      <c r="O129" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="O129" s="25" t="n"/>
       <c r="P129" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
       <c r="Q129" s="25" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="R129" s="25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S129" s="25" t="n">
         <v>2917.88</v>
@@ -21417,10 +21171,10 @@
         </is>
       </c>
       <c r="Q130" s="25" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="R130" s="25" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="S130" s="25" t="n">
         <v>3830.17</v>
@@ -21573,7 +21327,7 @@
         </is>
       </c>
       <c r="Q131" s="25" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="R131" s="25" t="n">
         <v>5</v>
@@ -21733,7 +21487,7 @@
         </is>
       </c>
       <c r="Q132" s="25" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="R132" s="25" t="n">
         <v>9</v>
@@ -21893,7 +21647,7 @@
         </is>
       </c>
       <c r="Q133" s="25" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="R133" s="25" t="n">
         <v>7</v>
@@ -22053,11 +21807,7 @@
         <v>1134.92</v>
       </c>
       <c r="O134" s="25" t="n"/>
-      <c r="P134" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P134" s="25" t="n"/>
       <c r="Q134" s="25" t="n"/>
       <c r="R134" s="25" t="n"/>
       <c r="S134" s="25" t="n"/>
@@ -22217,19 +21967,11 @@
         </is>
       </c>
       <c r="Q135" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="R135" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S135" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T135" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="R135" s="25" t="n"/>
+      <c r="S135" s="25" t="n"/>
+      <c r="T135" s="25" t="n"/>
       <c r="U135" s="25" t="n">
         <v>0</v>
       </c>
@@ -22376,24 +22118,20 @@
       <c r="N136" s="25" t="n">
         <v>656.45</v>
       </c>
-      <c r="O136" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P136" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="O136" s="25" t="n"/>
+      <c r="P136" s="25" t="n"/>
       <c r="Q136" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R136" s="25" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="R136" s="25" t="n"/>
       <c r="S136" s="25" t="n">
         <v>1391.63</v>
       </c>
-      <c r="T136" s="25" t="n"/>
+      <c r="T136" s="25" t="inlineStr">
+        <is>
+          <t>COMPRA B2B</t>
+        </is>
+      </c>
       <c r="U136" s="25" t="n">
         <v>1391.63</v>
       </c>
@@ -22545,7 +22283,7 @@
         </is>
       </c>
       <c r="Q137" s="25" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="R137" s="25" t="n">
         <v>7</v>
@@ -22701,7 +22439,7 @@
         </is>
       </c>
       <c r="Q138" s="25" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="R138" s="25" t="n">
         <v>4</v>
@@ -22861,11 +22599,7 @@
         <v>1932.83</v>
       </c>
       <c r="O139" s="25" t="n"/>
-      <c r="P139" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P139" s="25" t="n"/>
       <c r="Q139" s="25" t="n"/>
       <c r="R139" s="25" t="n"/>
       <c r="S139" s="25" t="n"/>
@@ -23013,10 +22747,10 @@
         </is>
       </c>
       <c r="Q140" s="25" t="n">
+        <v>26</v>
+      </c>
+      <c r="R140" s="25" t="n">
         <v>4</v>
-      </c>
-      <c r="R140" s="25" t="n">
-        <v>0</v>
       </c>
       <c r="S140" s="25" t="n">
         <v>5107.1</v>
@@ -23181,10 +22915,10 @@
         </is>
       </c>
       <c r="Q141" s="25" t="n">
-        <v>7</v>
+        <v>120</v>
       </c>
       <c r="R141" s="25" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="S141" s="25" t="n">
         <v>7858.08</v>
@@ -23345,11 +23079,7 @@
         <v>1152</v>
       </c>
       <c r="O142" s="25" t="n"/>
-      <c r="P142" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P142" s="25" t="n"/>
       <c r="Q142" s="25" t="n"/>
       <c r="R142" s="25" t="n"/>
       <c r="S142" s="25" t="n"/>
@@ -23509,7 +23239,7 @@
         </is>
       </c>
       <c r="Q143" s="25" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="R143" s="25" t="n">
         <v>16</v>
@@ -23681,10 +23411,10 @@
         </is>
       </c>
       <c r="Q144" s="25" t="n">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="R144" s="25" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="S144" s="25" t="n">
         <v>2303.38</v>
@@ -23853,10 +23583,10 @@
         </is>
       </c>
       <c r="Q145" s="25" t="n">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="R145" s="25" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="S145" s="25" t="n">
         <v>4396.27</v>
@@ -24021,7 +23751,7 @@
         </is>
       </c>
       <c r="Q146" s="25" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="R146" s="25" t="n">
         <v>17</v>
@@ -24194,7 +23924,7 @@
         </is>
       </c>
       <c r="Q147" s="25" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="R147" s="25" t="n">
         <v>11</v>
@@ -24362,10 +24092,10 @@
         </is>
       </c>
       <c r="Q148" s="25" t="n">
-        <v>48</v>
+        <v>337</v>
       </c>
       <c r="R148" s="25" t="n">
-        <v>254.48</v>
+        <v>42</v>
       </c>
       <c r="S148" s="25" t="n">
         <v>1199.04</v>
@@ -24526,11 +24256,7 @@
         <v>1998.41</v>
       </c>
       <c r="O149" s="25" t="n"/>
-      <c r="P149" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P149" s="25" t="n"/>
       <c r="Q149" s="25" t="n"/>
       <c r="R149" s="25" t="n"/>
       <c r="S149" s="25" t="n"/>
@@ -24690,7 +24416,7 @@
         </is>
       </c>
       <c r="Q150" s="25" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="R150" s="25" t="n">
         <v>12</v>
@@ -24858,13 +24584,13 @@
         </is>
       </c>
       <c r="Q151" s="25" t="n">
-        <v>17</v>
+        <v>284</v>
       </c>
       <c r="R151" s="25" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="S151" s="25" t="n">
-        <v>9250.18</v>
+        <v>6206.41</v>
       </c>
       <c r="T151" s="25" t="inlineStr">
         <is>
@@ -25026,10 +24752,10 @@
         </is>
       </c>
       <c r="Q152" s="25" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="R152" s="25" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S152" s="25" t="n">
         <v>430.26</v>
@@ -25186,11 +24912,7 @@
         <v>1693.08</v>
       </c>
       <c r="O153" s="25" t="n"/>
-      <c r="P153" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P153" s="25" t="n"/>
       <c r="Q153" s="25" t="n"/>
       <c r="R153" s="25" t="n"/>
       <c r="S153" s="25" t="n"/>
@@ -25342,11 +25064,7 @@
         <v>1449.87</v>
       </c>
       <c r="O154" s="25" t="n"/>
-      <c r="P154" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P154" s="25" t="n"/>
       <c r="Q154" s="25" t="n"/>
       <c r="R154" s="25" t="n"/>
       <c r="S154" s="25" t="n"/>
@@ -25506,7 +25224,7 @@
         </is>
       </c>
       <c r="Q155" s="25" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="R155" s="25" t="n">
         <v>16</v>
@@ -25666,11 +25384,7 @@
         <v>1026.82</v>
       </c>
       <c r="O156" s="25" t="n"/>
-      <c r="P156" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P156" s="25" t="n"/>
       <c r="Q156" s="25" t="n"/>
       <c r="R156" s="25" t="n"/>
       <c r="S156" s="25" t="n"/>
@@ -25834,10 +25548,10 @@
         </is>
       </c>
       <c r="Q157" s="25" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="R157" s="25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S157" s="25" t="n">
         <v>3371.49</v>
@@ -26002,7 +25716,7 @@
         </is>
       </c>
       <c r="Q158" s="25" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="R158" s="25" t="n">
         <v>24</v>
@@ -26162,11 +25876,7 @@
         <v>4270.86</v>
       </c>
       <c r="O159" s="25" t="n"/>
-      <c r="P159" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P159" s="25" t="n"/>
       <c r="Q159" s="25" t="n"/>
       <c r="R159" s="25" t="n"/>
       <c r="S159" s="25" t="n"/>
@@ -26326,19 +26036,11 @@
         </is>
       </c>
       <c r="Q160" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="R160" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S160" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T160" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="R160" s="25" t="n"/>
+      <c r="S160" s="25" t="n"/>
+      <c r="T160" s="25" t="n"/>
       <c r="U160" s="25" t="n">
         <v>0</v>
       </c>
@@ -26486,25 +26188,11 @@
         <v>1154.73</v>
       </c>
       <c r="O161" s="25" t="n"/>
-      <c r="P161" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="Q161" s="25" t="n">
-        <v>16</v>
-      </c>
-      <c r="R161" s="25" t="n">
-        <v>3161.94</v>
-      </c>
-      <c r="S161" s="25" t="n">
-        <v>3274.94</v>
-      </c>
-      <c r="T161" s="25" t="inlineStr">
-        <is>
-          <t>COMPRA B2B</t>
-        </is>
-      </c>
+      <c r="P161" s="25" t="n"/>
+      <c r="Q161" s="25" t="n"/>
+      <c r="R161" s="25" t="n"/>
+      <c r="S161" s="25" t="n"/>
+      <c r="T161" s="25" t="n"/>
       <c r="U161" s="25" t="n">
         <v>0</v>
       </c>
@@ -26652,25 +26340,11 @@
         <v>397.43</v>
       </c>
       <c r="O162" s="25" t="n"/>
-      <c r="P162" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="Q162" s="25" t="n">
-        <v>16</v>
-      </c>
-      <c r="R162" s="25" t="n">
-        <v>3161.94</v>
-      </c>
-      <c r="S162" s="25" t="n">
-        <v>3274.94</v>
-      </c>
-      <c r="T162" s="25" t="inlineStr">
-        <is>
-          <t>COMPRA B2B</t>
-        </is>
-      </c>
+      <c r="P162" s="25" t="n"/>
+      <c r="Q162" s="25" t="n"/>
+      <c r="R162" s="25" t="n"/>
+      <c r="S162" s="25" t="n"/>
+      <c r="T162" s="25" t="n"/>
       <c r="U162" s="25" t="n">
         <v>0</v>
       </c>
@@ -26826,13 +26500,13 @@
         </is>
       </c>
       <c r="Q163" s="25" t="n">
-        <v>12</v>
+        <v>208</v>
       </c>
       <c r="R163" s="25" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="S163" s="25" t="n">
-        <v>5112.98</v>
+        <v>11210.68</v>
       </c>
       <c r="T163" s="25" t="inlineStr">
         <is>
@@ -26982,10 +26656,10 @@
         </is>
       </c>
       <c r="Q164" s="25" t="n">
-        <v>27</v>
+        <v>317</v>
       </c>
       <c r="R164" s="25" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="S164" s="25" t="n">
         <v>1497.49</v>
@@ -27142,11 +26816,7 @@
         <v>1368.08</v>
       </c>
       <c r="O165" s="25" t="n"/>
-      <c r="P165" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P165" s="25" t="n"/>
       <c r="Q165" s="25" t="n"/>
       <c r="R165" s="25" t="n"/>
       <c r="S165" s="25" t="n"/>
@@ -27302,11 +26972,7 @@
         <v>2536.11</v>
       </c>
       <c r="O166" s="25" t="n"/>
-      <c r="P166" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P166" s="25" t="n"/>
       <c r="Q166" s="25" t="n"/>
       <c r="R166" s="25" t="n"/>
       <c r="S166" s="25" t="n"/>
@@ -27458,11 +27124,7 @@
         <v>889.25</v>
       </c>
       <c r="O167" s="25" t="n"/>
-      <c r="P167" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P167" s="25" t="n"/>
       <c r="Q167" s="25" t="n"/>
       <c r="R167" s="25" t="n"/>
       <c r="S167" s="25" t="n"/>
@@ -27622,7 +27284,7 @@
         </is>
       </c>
       <c r="Q168" s="25" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="R168" s="25" t="n">
         <v>5</v>
@@ -27770,7 +27432,7 @@
         <v>2107.44</v>
       </c>
       <c r="O169" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P169" s="25" t="inlineStr">
         <is>
@@ -27778,10 +27440,10 @@
         </is>
       </c>
       <c r="Q169" s="25" t="n">
-        <v>6</v>
+        <v>181</v>
       </c>
       <c r="R169" s="25" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="S169" s="25" t="n">
         <v>2107.44</v>
@@ -27934,10 +27596,10 @@
         </is>
       </c>
       <c r="Q170" s="25" t="n">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="R170" s="25" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S170" s="25" t="n">
         <v>1748.86</v>
@@ -28102,19 +27764,13 @@
         </is>
       </c>
       <c r="Q171" s="25" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="R171" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="S171" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T171" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="S171" s="25" t="n"/>
+      <c r="T171" s="25" t="n"/>
       <c r="U171" s="25" t="n">
         <v>0</v>
       </c>
@@ -28270,10 +27926,10 @@
         </is>
       </c>
       <c r="Q172" s="25" t="n">
-        <v>13</v>
+        <v>217</v>
       </c>
       <c r="R172" s="25" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="S172" s="25" t="n">
         <v>2870.97</v>
@@ -28438,19 +28094,11 @@
         </is>
       </c>
       <c r="Q173" s="25" t="n">
-        <v>9</v>
-      </c>
-      <c r="R173" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S173" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T173" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="R173" s="25" t="n"/>
+      <c r="S173" s="25" t="n"/>
+      <c r="T173" s="25" t="n"/>
       <c r="U173" s="25" t="n">
         <v>0</v>
       </c>
@@ -28606,7 +28254,7 @@
         </is>
       </c>
       <c r="Q174" s="25" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="R174" s="25" t="n">
         <v>6</v>
@@ -28766,11 +28414,7 @@
         <v>3305.18</v>
       </c>
       <c r="O175" s="25" t="n"/>
-      <c r="P175" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P175" s="25" t="n"/>
       <c r="Q175" s="25" t="n"/>
       <c r="R175" s="25" t="n"/>
       <c r="S175" s="25" t="n"/>
@@ -28910,11 +28554,7 @@
         <v>2094.94</v>
       </c>
       <c r="O176" s="25" t="n"/>
-      <c r="P176" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P176" s="25" t="n"/>
       <c r="Q176" s="25" t="n"/>
       <c r="R176" s="25" t="n"/>
       <c r="S176" s="25" t="n"/>
@@ -29074,7 +28714,7 @@
         </is>
       </c>
       <c r="Q177" s="25" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="R177" s="25" t="n">
         <v>33</v>
@@ -29230,7 +28870,7 @@
         </is>
       </c>
       <c r="Q178" s="25" t="n">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="R178" s="25" t="n">
         <v>19</v>
@@ -29390,7 +29030,7 @@
         <v>815.75</v>
       </c>
       <c r="O179" s="25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P179" s="25" t="inlineStr">
         <is>
@@ -29398,10 +29038,10 @@
         </is>
       </c>
       <c r="Q179" s="25" t="n">
-        <v>22</v>
+        <v>217</v>
       </c>
       <c r="R179" s="25" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="S179" s="25" t="n">
         <v>3300.25</v>
@@ -29566,10 +29206,10 @@
         </is>
       </c>
       <c r="Q180" s="25" t="n">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="R180" s="25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S180" s="25" t="n">
         <v>1513.57</v>
@@ -29730,11 +29370,7 @@
         <v>2536.11</v>
       </c>
       <c r="O181" s="25" t="n"/>
-      <c r="P181" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P181" s="25" t="n"/>
       <c r="Q181" s="25" t="n"/>
       <c r="R181" s="25" t="n"/>
       <c r="S181" s="25" t="n"/>
@@ -29890,11 +29526,7 @@
         <v>1174.05</v>
       </c>
       <c r="O182" s="25" t="n"/>
-      <c r="P182" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P182" s="25" t="n"/>
       <c r="Q182" s="25" t="n"/>
       <c r="R182" s="25" t="n"/>
       <c r="S182" s="25" t="n"/>
@@ -30049,19 +29681,17 @@
       <c r="N183" s="25" t="n">
         <v>677.73</v>
       </c>
-      <c r="O183" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="O183" s="25" t="n"/>
       <c r="P183" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
       <c r="Q183" s="25" t="n">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="R183" s="25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S183" s="25" t="n">
         <v>1280.73</v>
@@ -30226,10 +29856,10 @@
         </is>
       </c>
       <c r="Q184" s="25" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="R184" s="25" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="S184" s="25" t="n">
         <v>1329.92</v>
@@ -30382,10 +30012,10 @@
         </is>
       </c>
       <c r="Q185" s="25" t="n">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="R185" s="25" t="n">
-        <v>467.81</v>
+        <v>13</v>
       </c>
       <c r="S185" s="25" t="n">
         <v>1055.68</v>
@@ -30550,10 +30180,10 @@
         </is>
       </c>
       <c r="Q186" s="25" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="R186" s="25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S186" s="25" t="n">
         <v>1019.96</v>
@@ -30706,7 +30336,7 @@
         </is>
       </c>
       <c r="Q187" s="25" t="n">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="R187" s="25" t="n">
         <v>7</v>
@@ -30866,10 +30496,10 @@
         </is>
       </c>
       <c r="Q188" s="25" t="n">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="R188" s="25" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="S188" s="25" t="n">
         <v>2119.66</v>
@@ -31024,17 +30654,9 @@
       <c r="Q189" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="R189" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S189" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T189" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="R189" s="25" t="n"/>
+      <c r="S189" s="25" t="n"/>
+      <c r="T189" s="25" t="n"/>
       <c r="U189" s="25" t="n">
         <v>0</v>
       </c>
@@ -31190,19 +30812,11 @@
         </is>
       </c>
       <c r="Q190" s="25" t="n">
-        <v>20</v>
-      </c>
-      <c r="R190" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S190" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T190" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="R190" s="25" t="n"/>
+      <c r="S190" s="25" t="n"/>
+      <c r="T190" s="25" t="n"/>
       <c r="U190" s="25" t="n">
         <v>0</v>
       </c>
@@ -31358,19 +30972,11 @@
         </is>
       </c>
       <c r="Q191" s="25" t="n">
-        <v>7</v>
-      </c>
-      <c r="R191" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S191" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T191" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="R191" s="25" t="n"/>
+      <c r="S191" s="25" t="n"/>
+      <c r="T191" s="25" t="n"/>
       <c r="U191" s="25" t="n">
         <v>2281.3</v>
       </c>
@@ -31526,7 +31132,7 @@
         </is>
       </c>
       <c r="Q192" s="25" t="n">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="R192" s="25" t="n">
         <v>38</v>
@@ -31686,11 +31292,7 @@
         <v>576</v>
       </c>
       <c r="O193" s="25" t="n"/>
-      <c r="P193" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P193" s="25" t="n"/>
       <c r="Q193" s="25" t="n"/>
       <c r="R193" s="25" t="n"/>
       <c r="S193" s="25" t="n"/>
@@ -31850,19 +31452,11 @@
         </is>
       </c>
       <c r="Q194" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="R194" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S194" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T194" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="R194" s="25" t="n"/>
+      <c r="S194" s="25" t="n"/>
+      <c r="T194" s="25" t="n"/>
       <c r="U194" s="25" t="n">
         <v>0</v>
       </c>
@@ -32018,7 +31612,7 @@
         </is>
       </c>
       <c r="Q195" s="25" t="n">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="R195" s="25" t="n">
         <v>5</v>
@@ -32186,19 +31780,11 @@
         </is>
       </c>
       <c r="Q196" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="R196" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S196" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T196" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="R196" s="25" t="n"/>
+      <c r="S196" s="25" t="n"/>
+      <c r="T196" s="25" t="n"/>
       <c r="U196" s="25" t="n">
         <v>0</v>
       </c>
@@ -32342,11 +31928,7 @@
         <v>398.62</v>
       </c>
       <c r="O197" s="25" t="n"/>
-      <c r="P197" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P197" s="25" t="n"/>
       <c r="Q197" s="25" t="n"/>
       <c r="R197" s="25" t="n"/>
       <c r="S197" s="25" t="n"/>
@@ -32494,19 +32076,11 @@
         </is>
       </c>
       <c r="Q198" s="25" t="n">
-        <v>21</v>
-      </c>
-      <c r="R198" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S198" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T198" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="R198" s="25" t="n"/>
+      <c r="S198" s="25" t="n"/>
+      <c r="T198" s="25" t="n"/>
       <c r="U198" s="25" t="n">
         <v>0</v>
       </c>
@@ -32662,19 +32236,11 @@
         </is>
       </c>
       <c r="Q199" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="R199" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S199" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T199" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="R199" s="25" t="n"/>
+      <c r="S199" s="25" t="n"/>
+      <c r="T199" s="25" t="n"/>
       <c r="U199" s="25" t="n">
         <v>0</v>
       </c>
@@ -32830,7 +32396,7 @@
         </is>
       </c>
       <c r="Q200" s="25" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="R200" s="25" t="n">
         <v>3</v>
@@ -33003,7 +32569,7 @@
         </is>
       </c>
       <c r="Q201" s="25" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="R201" s="25" t="n">
         <v>21</v>
@@ -33171,7 +32737,7 @@
         </is>
       </c>
       <c r="Q202" s="25" t="n">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="R202" s="25" t="n">
         <v>10</v>
@@ -33339,19 +32905,13 @@
         </is>
       </c>
       <c r="Q203" s="25" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="R203" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="S203" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T203" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="S203" s="25" t="n"/>
+      <c r="T203" s="25" t="n"/>
       <c r="U203" s="25" t="n">
         <v>0</v>
       </c>
@@ -33507,10 +33067,10 @@
         </is>
       </c>
       <c r="Q204" s="25" t="n">
-        <v>5</v>
+        <v>96</v>
       </c>
       <c r="R204" s="25" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="S204" s="25" t="n">
         <v>1781.87</v>
@@ -33671,11 +33231,7 @@
         <v>3742.44</v>
       </c>
       <c r="O205" s="25" t="n"/>
-      <c r="P205" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P205" s="25" t="n"/>
       <c r="Q205" s="25" t="n"/>
       <c r="R205" s="25" t="n"/>
       <c r="S205" s="25" t="n"/>
@@ -33819,11 +33375,7 @@
         <v>1213.9</v>
       </c>
       <c r="O206" s="25" t="n"/>
-      <c r="P206" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P206" s="25" t="n"/>
       <c r="Q206" s="25" t="n"/>
       <c r="R206" s="25" t="n"/>
       <c r="S206" s="25" t="n"/>
@@ -33983,19 +33535,11 @@
         </is>
       </c>
       <c r="Q207" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R207" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S207" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T207" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="R207" s="25" t="n"/>
+      <c r="S207" s="25" t="n"/>
+      <c r="T207" s="25" t="n"/>
       <c r="U207" s="25" t="n">
         <v>0</v>
       </c>
@@ -34151,10 +33695,10 @@
         </is>
       </c>
       <c r="Q208" s="25" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="R208" s="25" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="S208" s="25" t="n">
         <v>4872.89</v>
@@ -34319,19 +33863,11 @@
         </is>
       </c>
       <c r="Q209" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="R209" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S209" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T209" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="R209" s="25" t="n"/>
+      <c r="S209" s="25" t="n"/>
+      <c r="T209" s="25" t="n"/>
       <c r="U209" s="25" t="n">
         <v>0</v>
       </c>
@@ -34479,11 +34015,7 @@
         <v>2170.59</v>
       </c>
       <c r="O210" s="25" t="n"/>
-      <c r="P210" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P210" s="25" t="n"/>
       <c r="Q210" s="25" t="n"/>
       <c r="R210" s="25" t="n"/>
       <c r="S210" s="25" t="n"/>
@@ -34635,11 +34167,7 @@
         <v>3510.38</v>
       </c>
       <c r="O211" s="25" t="n"/>
-      <c r="P211" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P211" s="25" t="n"/>
       <c r="Q211" s="25" t="n"/>
       <c r="R211" s="25" t="n"/>
       <c r="S211" s="25" t="n"/>
@@ -34791,11 +34319,7 @@
         <v>810.36</v>
       </c>
       <c r="O212" s="25" t="n"/>
-      <c r="P212" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P212" s="25" t="n"/>
       <c r="Q212" s="25" t="n"/>
       <c r="R212" s="25" t="n"/>
       <c r="S212" s="25" t="n"/>
@@ -34939,11 +34463,7 @@
         <v>986.3200000000001</v>
       </c>
       <c r="O213" s="25" t="n"/>
-      <c r="P213" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P213" s="25" t="n"/>
       <c r="Q213" s="25" t="n"/>
       <c r="R213" s="25" t="n"/>
       <c r="S213" s="25" t="n"/>
@@ -35099,7 +34619,7 @@
         <v>678</v>
       </c>
       <c r="O214" s="25" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="P214" s="25" t="inlineStr">
         <is>
@@ -35107,13 +34627,13 @@
         </is>
       </c>
       <c r="Q214" s="25" t="n">
-        <v>14</v>
+        <v>296</v>
       </c>
       <c r="R214" s="25" t="n">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="S214" s="25" t="n">
-        <v>678</v>
+        <v>1462.09</v>
       </c>
       <c r="T214" s="25" t="inlineStr">
         <is>
@@ -35275,7 +34795,7 @@
         </is>
       </c>
       <c r="Q215" s="25" t="n">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="R215" s="25" t="n">
         <v>19</v>
@@ -35439,23 +34959,15 @@
       </c>
       <c r="P216" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="Q216" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="R216" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S216" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T216" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="R216" s="25" t="n"/>
+      <c r="S216" s="25" t="n"/>
+      <c r="T216" s="25" t="n"/>
       <c r="U216" s="25" t="n">
         <v>0</v>
       </c>
@@ -35611,13 +35123,13 @@
         </is>
       </c>
       <c r="Q217" s="25" t="n">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="R217" s="25" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S217" s="25" t="n">
-        <v>7803.63</v>
+        <v>4280.81</v>
       </c>
       <c r="T217" s="25" t="inlineStr">
         <is>
@@ -35771,11 +35283,7 @@
         <v>6491.55</v>
       </c>
       <c r="O218" s="25" t="n"/>
-      <c r="P218" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P218" s="25" t="n"/>
       <c r="Q218" s="25" t="n"/>
       <c r="R218" s="25" t="n"/>
       <c r="S218" s="25" t="n"/>
@@ -35935,19 +35443,11 @@
         </is>
       </c>
       <c r="Q219" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R219" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S219" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T219" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="R219" s="25" t="n"/>
+      <c r="S219" s="25" t="n"/>
+      <c r="T219" s="25" t="n"/>
       <c r="U219" s="25" t="n">
         <v>0</v>
       </c>
@@ -36103,10 +35603,10 @@
         </is>
       </c>
       <c r="Q220" s="25" t="n">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="R220" s="25" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S220" s="25" t="n">
         <v>1029.55</v>
@@ -36263,11 +35763,7 @@
         <v>2127.96</v>
       </c>
       <c r="O221" s="25" t="n"/>
-      <c r="P221" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P221" s="25" t="n"/>
       <c r="Q221" s="25" t="n"/>
       <c r="R221" s="25" t="n"/>
       <c r="S221" s="25" t="n"/>
@@ -36419,11 +35915,7 @@
         <v>4509.1</v>
       </c>
       <c r="O222" s="25" t="n"/>
-      <c r="P222" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P222" s="25" t="n"/>
       <c r="Q222" s="25" t="n"/>
       <c r="R222" s="25" t="n"/>
       <c r="S222" s="25" t="n"/>
@@ -36575,11 +36067,7 @@
         <v>9180</v>
       </c>
       <c r="O223" s="25" t="n"/>
-      <c r="P223" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P223" s="25" t="n"/>
       <c r="Q223" s="25" t="n"/>
       <c r="R223" s="25" t="n"/>
       <c r="S223" s="25" t="n"/>
@@ -36731,11 +36219,7 @@
         <v>1950</v>
       </c>
       <c r="O224" s="25" t="n"/>
-      <c r="P224" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P224" s="25" t="n"/>
       <c r="Q224" s="25" t="n"/>
       <c r="R224" s="25" t="n"/>
       <c r="S224" s="25" t="n"/>
@@ -36899,13 +36383,13 @@
         </is>
       </c>
       <c r="Q225" s="25" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="R225" s="25" t="n">
         <v>29</v>
       </c>
       <c r="S225" s="25" t="n">
-        <v>3104.22</v>
+        <v>1552.11</v>
       </c>
       <c r="T225" s="25" t="inlineStr">
         <is>
@@ -37067,13 +36551,13 @@
         </is>
       </c>
       <c r="Q226" s="25" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="R226" s="25" t="n">
         <v>25</v>
       </c>
       <c r="S226" s="25" t="n">
-        <v>3052</v>
+        <v>1526</v>
       </c>
       <c r="T226" s="25" t="inlineStr">
         <is>
@@ -37239,13 +36723,13 @@
         </is>
       </c>
       <c r="Q227" s="25" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="R227" s="25" t="n">
         <v>23</v>
       </c>
       <c r="S227" s="25" t="n">
-        <v>2180.1</v>
+        <v>1090.05</v>
       </c>
       <c r="T227" s="25" t="inlineStr">
         <is>
@@ -37411,7 +36895,7 @@
         </is>
       </c>
       <c r="Q228" s="25" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="R228" s="25" t="n">
         <v>13</v>
@@ -37588,7 +37072,7 @@
         </is>
       </c>
       <c r="Q229" s="25" t="n">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="R229" s="25" t="n">
         <v>22</v>
@@ -37757,11 +37241,7 @@
         <v>2664.61</v>
       </c>
       <c r="O230" s="25" t="n"/>
-      <c r="P230" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P230" s="25" t="n"/>
       <c r="Q230" s="25" t="n"/>
       <c r="R230" s="25" t="n"/>
       <c r="S230" s="25" t="n"/>
@@ -37921,19 +37401,13 @@
         </is>
       </c>
       <c r="Q231" s="25" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="R231" s="25" t="n">
         <v>15</v>
       </c>
-      <c r="S231" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T231" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="S231" s="25" t="n"/>
+      <c r="T231" s="25" t="n"/>
       <c r="U231" s="25" t="n">
         <v>0</v>
       </c>
@@ -38081,11 +37555,7 @@
         <v>990.28</v>
       </c>
       <c r="O232" s="25" t="n"/>
-      <c r="P232" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P232" s="25" t="n"/>
       <c r="Q232" s="25" t="n"/>
       <c r="R232" s="25" t="n"/>
       <c r="S232" s="25" t="n"/>
@@ -38237,11 +37707,7 @@
         <v>696.96</v>
       </c>
       <c r="O233" s="25" t="n"/>
-      <c r="P233" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P233" s="25" t="n"/>
       <c r="Q233" s="25" t="n"/>
       <c r="R233" s="25" t="n"/>
       <c r="S233" s="25" t="n"/>
@@ -38393,11 +37859,7 @@
         <v>16230.4</v>
       </c>
       <c r="O234" s="25" t="n"/>
-      <c r="P234" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P234" s="25" t="n"/>
       <c r="Q234" s="25" t="n"/>
       <c r="R234" s="25" t="n"/>
       <c r="S234" s="25" t="n"/>
@@ -38553,11 +38015,7 @@
         <v>1618.97</v>
       </c>
       <c r="O235" s="25" t="n"/>
-      <c r="P235" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P235" s="25" t="n"/>
       <c r="Q235" s="25" t="n"/>
       <c r="R235" s="25" t="n"/>
       <c r="S235" s="25" t="n"/>
@@ -38709,11 +38167,7 @@
         <v>766.02</v>
       </c>
       <c r="O236" s="25" t="n"/>
-      <c r="P236" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P236" s="25" t="n"/>
       <c r="Q236" s="25" t="n"/>
       <c r="R236" s="25" t="n"/>
       <c r="S236" s="25" t="n"/>
@@ -38865,11 +38319,7 @@
         <v>678.53</v>
       </c>
       <c r="O237" s="25" t="n"/>
-      <c r="P237" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P237" s="25" t="n"/>
       <c r="Q237" s="25" t="n"/>
       <c r="R237" s="25" t="n"/>
       <c r="S237" s="25" t="n"/>
@@ -39029,7 +38479,7 @@
         </is>
       </c>
       <c r="Q238" s="25" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="R238" s="25" t="n">
         <v>17</v>
@@ -39189,11 +38639,7 @@
         <v>3060.88</v>
       </c>
       <c r="O239" s="25" t="n"/>
-      <c r="P239" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P239" s="25" t="n"/>
       <c r="Q239" s="25" t="n"/>
       <c r="R239" s="25" t="n"/>
       <c r="S239" s="25" t="n"/>
@@ -39353,7 +38799,7 @@
         </is>
       </c>
       <c r="Q240" s="25" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="R240" s="25" t="n">
         <v>19</v>
@@ -39523,17 +38969,9 @@
       <c r="Q241" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="R241" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S241" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T241" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="R241" s="25" t="n"/>
+      <c r="S241" s="25" t="n"/>
+      <c r="T241" s="25" t="n"/>
       <c r="U241" s="25" t="n">
         <v>0</v>
       </c>
@@ -39681,11 +39119,7 @@
         <v>681.48</v>
       </c>
       <c r="O242" s="25" t="n"/>
-      <c r="P242" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P242" s="25" t="n"/>
       <c r="Q242" s="25" t="n"/>
       <c r="R242" s="25" t="n"/>
       <c r="S242" s="25" t="n"/>
@@ -39845,10 +39279,10 @@
         </is>
       </c>
       <c r="Q243" s="25" t="n">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="R243" s="25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S243" s="25" t="n">
         <v>659.3</v>
@@ -40017,19 +39451,13 @@
         </is>
       </c>
       <c r="Q244" s="25" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="R244" s="25" t="n">
         <v>13</v>
       </c>
-      <c r="S244" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T244" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="S244" s="25" t="n"/>
+      <c r="T244" s="25" t="n"/>
       <c r="U244" s="25" t="n">
         <v>0</v>
       </c>
@@ -40177,11 +39605,7 @@
         <v>3912.71</v>
       </c>
       <c r="O245" s="25" t="n"/>
-      <c r="P245" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P245" s="25" t="n"/>
       <c r="Q245" s="25" t="n"/>
       <c r="R245" s="25" t="n"/>
       <c r="S245" s="25" t="n"/>
@@ -40333,11 +39757,7 @@
         <v>963.58</v>
       </c>
       <c r="O246" s="25" t="n"/>
-      <c r="P246" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P246" s="25" t="n"/>
       <c r="Q246" s="25" t="n"/>
       <c r="R246" s="25" t="n"/>
       <c r="S246" s="25" t="n"/>
@@ -40489,11 +39909,7 @@
         <v>2968.21</v>
       </c>
       <c r="O247" s="25" t="n"/>
-      <c r="P247" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P247" s="25" t="n"/>
       <c r="Q247" s="25" t="n"/>
       <c r="R247" s="25" t="n"/>
       <c r="S247" s="25" t="n"/>
@@ -40645,11 +40061,7 @@
         <v>1442.87</v>
       </c>
       <c r="O248" s="25" t="n"/>
-      <c r="P248" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P248" s="25" t="n"/>
       <c r="Q248" s="25" t="n"/>
       <c r="R248" s="25" t="n"/>
       <c r="S248" s="25" t="n"/>
@@ -40809,19 +40221,11 @@
         </is>
       </c>
       <c r="Q249" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R249" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S249" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T249" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="R249" s="25" t="n"/>
+      <c r="S249" s="25" t="n"/>
+      <c r="T249" s="25" t="n"/>
       <c r="U249" s="25" t="n">
         <v>0</v>
       </c>
@@ -40973,11 +40377,7 @@
         <v>1060.55</v>
       </c>
       <c r="O250" s="25" t="n"/>
-      <c r="P250" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P250" s="25" t="n"/>
       <c r="Q250" s="25" t="n"/>
       <c r="R250" s="25" t="n"/>
       <c r="S250" s="25" t="n"/>
@@ -41133,11 +40533,7 @@
         <v>1003.77</v>
       </c>
       <c r="O251" s="25" t="n"/>
-      <c r="P251" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P251" s="25" t="n"/>
       <c r="Q251" s="25" t="n"/>
       <c r="R251" s="25" t="n"/>
       <c r="S251" s="25" t="n"/>
@@ -41281,11 +40677,7 @@
         <v>1003.77</v>
       </c>
       <c r="O252" s="25" t="n"/>
-      <c r="P252" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P252" s="25" t="n"/>
       <c r="Q252" s="25" t="n"/>
       <c r="R252" s="25" t="n"/>
       <c r="S252" s="25" t="n"/>
@@ -41441,11 +40833,7 @@
         <v>1400.94</v>
       </c>
       <c r="O253" s="25" t="n"/>
-      <c r="P253" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P253" s="25" t="n"/>
       <c r="Q253" s="25" t="n"/>
       <c r="R253" s="25" t="n"/>
       <c r="S253" s="25" t="n"/>
@@ -41600,13 +40988,17 @@
       <c r="N254" s="25" t="n">
         <v>1160.25</v>
       </c>
-      <c r="O254" s="25" t="n"/>
+      <c r="O254" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="P254" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="Q254" s="25" t="n"/>
+      <c r="Q254" s="25" t="n">
+        <v>12</v>
+      </c>
       <c r="R254" s="25" t="n"/>
       <c r="S254" s="25" t="n"/>
       <c r="T254" s="25" t="n"/>
@@ -41757,7 +41149,7 @@
         </is>
       </c>
       <c r="Q255" s="25" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="R255" s="25" t="n">
         <v>2</v>
@@ -41921,11 +41313,7 @@
         <v>696.5</v>
       </c>
       <c r="O256" s="25" t="n"/>
-      <c r="P256" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P256" s="25" t="n"/>
       <c r="Q256" s="25" t="n"/>
       <c r="R256" s="25" t="n"/>
       <c r="S256" s="25" t="n"/>
@@ -42081,11 +41469,7 @@
         <v>6306.96</v>
       </c>
       <c r="O257" s="25" t="n"/>
-      <c r="P257" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P257" s="25" t="n"/>
       <c r="Q257" s="25" t="n"/>
       <c r="R257" s="25" t="n"/>
       <c r="S257" s="25" t="n"/>
@@ -42237,11 +41621,7 @@
         <v>9404.709999999999</v>
       </c>
       <c r="O258" s="25" t="n"/>
-      <c r="P258" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P258" s="25" t="n"/>
       <c r="Q258" s="25" t="n"/>
       <c r="R258" s="25" t="n"/>
       <c r="S258" s="25" t="n"/>
@@ -42401,7 +41781,7 @@
         </is>
       </c>
       <c r="Q259" s="25" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="R259" s="25" t="n">
         <v>19</v>
@@ -42569,7 +41949,7 @@
         </is>
       </c>
       <c r="Q260" s="25" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="R260" s="25" t="n">
         <v>15</v>
@@ -42729,11 +42109,7 @@
         <v>1809</v>
       </c>
       <c r="O261" s="25" t="n"/>
-      <c r="P261" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P261" s="25" t="n"/>
       <c r="Q261" s="25" t="n"/>
       <c r="R261" s="25" t="n"/>
       <c r="S261" s="25" t="n"/>
@@ -42893,7 +42269,7 @@
         </is>
       </c>
       <c r="Q262" s="25" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="R262" s="25" t="n">
         <v>21</v>
@@ -43065,19 +42441,11 @@
         </is>
       </c>
       <c r="Q263" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="R263" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S263" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T263" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="R263" s="25" t="n"/>
+      <c r="S263" s="25" t="n"/>
+      <c r="T263" s="25" t="n"/>
       <c r="U263" s="25" t="n">
         <v>0</v>
       </c>
@@ -43238,13 +42606,13 @@
         </is>
       </c>
       <c r="Q264" s="25" t="n">
-        <v>4</v>
+        <v>110</v>
       </c>
       <c r="R264" s="25" t="n">
         <v>41</v>
       </c>
       <c r="S264" s="25" t="n">
-        <v>5427.72</v>
+        <v>2713.86</v>
       </c>
       <c r="T264" s="25" t="inlineStr">
         <is>
@@ -43406,19 +42774,11 @@
         </is>
       </c>
       <c r="Q265" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="R265" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S265" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T265" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="R265" s="25" t="n"/>
+      <c r="S265" s="25" t="n"/>
+      <c r="T265" s="25" t="n"/>
       <c r="U265" s="25" t="n">
         <v>0</v>
       </c>
@@ -43574,10 +42934,10 @@
         </is>
       </c>
       <c r="Q266" s="25" t="n">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="R266" s="25" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="S266" s="25" t="n">
         <v>1993.34</v>
@@ -43739,11 +43099,7 @@
         <v>3451.19</v>
       </c>
       <c r="O267" s="25" t="n"/>
-      <c r="P267" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P267" s="25" t="n"/>
       <c r="Q267" s="25" t="n"/>
       <c r="R267" s="25" t="n"/>
       <c r="S267" s="25" t="n"/>
@@ -43898,14 +43254,20 @@
       <c r="N268" s="25" t="n">
         <v>1036.87</v>
       </c>
-      <c r="O268" s="25" t="n"/>
+      <c r="O268" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="P268" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="Q268" s="25" t="n"/>
-      <c r="R268" s="25" t="n"/>
+      <c r="Q268" s="25" t="n">
+        <v>145</v>
+      </c>
+      <c r="R268" s="25" t="n">
+        <v>25</v>
+      </c>
       <c r="S268" s="25" t="n"/>
       <c r="T268" s="25" t="n"/>
       <c r="U268" s="25" t="n">
@@ -44067,7 +43429,7 @@
         </is>
       </c>
       <c r="Q269" s="25" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="R269" s="25" t="n">
         <v>26</v>
@@ -44239,7 +43601,7 @@
         </is>
       </c>
       <c r="Q270" s="25" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="R270" s="25" t="n">
         <v>8</v>
@@ -44399,11 +43761,7 @@
         <v>1648.08</v>
       </c>
       <c r="O271" s="25" t="n"/>
-      <c r="P271" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P271" s="25" t="n"/>
       <c r="Q271" s="25" t="n"/>
       <c r="R271" s="25" t="n"/>
       <c r="S271" s="25" t="n"/>
@@ -44559,11 +43917,7 @@
         <v>1418.16</v>
       </c>
       <c r="O272" s="25" t="n"/>
-      <c r="P272" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P272" s="25" t="n"/>
       <c r="Q272" s="25" t="n"/>
       <c r="R272" s="25" t="n"/>
       <c r="S272" s="25" t="n"/>
@@ -44715,11 +44069,7 @@
         <v>1130.72</v>
       </c>
       <c r="O273" s="25" t="n"/>
-      <c r="P273" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P273" s="25" t="n"/>
       <c r="Q273" s="25" t="n"/>
       <c r="R273" s="25" t="n"/>
       <c r="S273" s="25" t="n"/>
@@ -44875,11 +44225,7 @@
         <v>1180.52</v>
       </c>
       <c r="O274" s="25" t="n"/>
-      <c r="P274" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P274" s="25" t="n"/>
       <c r="Q274" s="25" t="n"/>
       <c r="R274" s="25" t="n"/>
       <c r="S274" s="25" t="n"/>
@@ -45035,11 +44381,7 @@
         <v>1649.94</v>
       </c>
       <c r="O275" s="25" t="n"/>
-      <c r="P275" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P275" s="25" t="n"/>
       <c r="Q275" s="25" t="n"/>
       <c r="R275" s="25" t="n"/>
       <c r="S275" s="25" t="n"/>
@@ -45191,11 +44533,7 @@
         <v>1131.79</v>
       </c>
       <c r="O276" s="25" t="n"/>
-      <c r="P276" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P276" s="25" t="n"/>
       <c r="Q276" s="25" t="n"/>
       <c r="R276" s="25" t="n"/>
       <c r="S276" s="25" t="n"/>
@@ -45347,7 +44685,7 @@
         </is>
       </c>
       <c r="Q277" s="25" t="n">
-        <v>4</v>
+        <v>146</v>
       </c>
       <c r="R277" s="25" t="n">
         <v>38</v>
@@ -45507,13 +44845,13 @@
         </is>
       </c>
       <c r="Q278" s="25" t="n">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="R278" s="25" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="S278" s="25" t="n">
-        <v>3279.98</v>
+        <v>2350.41</v>
       </c>
       <c r="T278" s="25" t="inlineStr">
         <is>
@@ -45675,10 +45013,10 @@
         </is>
       </c>
       <c r="Q279" s="25" t="n">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="R279" s="25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S279" s="25" t="n">
         <v>2314.17</v>
@@ -45843,13 +45181,13 @@
         </is>
       </c>
       <c r="Q280" s="25" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="R280" s="25" t="n">
         <v>7</v>
       </c>
       <c r="S280" s="25" t="n">
-        <v>1355.4</v>
+        <v>677.7</v>
       </c>
       <c r="T280" s="25" t="inlineStr">
         <is>
@@ -46011,7 +45349,7 @@
         </is>
       </c>
       <c r="Q281" s="25" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="R281" s="25" t="n">
         <v>7</v>
@@ -46171,11 +45509,7 @@
         <v>1606.83</v>
       </c>
       <c r="O282" s="25" t="n"/>
-      <c r="P282" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P282" s="25" t="n"/>
       <c r="Q282" s="25" t="n"/>
       <c r="R282" s="25" t="n"/>
       <c r="S282" s="25" t="n"/>
@@ -46327,7 +45661,7 @@
         <v>657.3200000000001</v>
       </c>
       <c r="O283" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P283" s="25" t="inlineStr">
         <is>
@@ -46335,13 +45669,13 @@
         </is>
       </c>
       <c r="Q283" s="25" t="n">
-        <v>24</v>
+        <v>171</v>
       </c>
       <c r="R283" s="25" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="S283" s="25" t="n">
-        <v>4573.27</v>
+        <v>3436.97</v>
       </c>
       <c r="T283" s="25" t="inlineStr">
         <is>
@@ -46503,10 +45837,10 @@
         </is>
       </c>
       <c r="Q284" s="25" t="n">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="R284" s="25" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="S284" s="25" t="n">
         <v>1543.95</v>
@@ -46663,11 +45997,7 @@
         <v>1439.93</v>
       </c>
       <c r="O285" s="25" t="n"/>
-      <c r="P285" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P285" s="25" t="n"/>
       <c r="Q285" s="25" t="n"/>
       <c r="R285" s="25" t="n"/>
       <c r="S285" s="25" t="n"/>
@@ -46819,11 +46149,7 @@
         <v>1215.54</v>
       </c>
       <c r="O286" s="25" t="n"/>
-      <c r="P286" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P286" s="25" t="n"/>
       <c r="Q286" s="25" t="n"/>
       <c r="R286" s="25" t="n"/>
       <c r="S286" s="25" t="n"/>
@@ -46975,7 +46301,7 @@
         <v>712.46</v>
       </c>
       <c r="O287" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P287" s="25" t="inlineStr">
         <is>
@@ -46983,10 +46309,10 @@
         </is>
       </c>
       <c r="Q287" s="25" t="n">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="R287" s="25" t="n">
-        <v>455.3</v>
+        <v>13</v>
       </c>
       <c r="S287" s="25" t="n">
         <v>701.58</v>
@@ -47151,10 +46477,10 @@
         </is>
       </c>
       <c r="Q288" s="25" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="R288" s="25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S288" s="25" t="n">
         <v>5772.73</v>
@@ -47319,10 +46645,10 @@
         </is>
       </c>
       <c r="Q289" s="25" t="n">
-        <v>6</v>
+        <v>151</v>
       </c>
       <c r="R289" s="25" t="n">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="S289" s="25" t="n">
         <v>4040.65</v>
@@ -47479,11 +46805,7 @@
         <v>684.92</v>
       </c>
       <c r="O290" s="25" t="n"/>
-      <c r="P290" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P290" s="25" t="n"/>
       <c r="Q290" s="25" t="n"/>
       <c r="R290" s="25" t="n"/>
       <c r="S290" s="25" t="n"/>
@@ -47643,10 +46965,10 @@
         </is>
       </c>
       <c r="Q291" s="25" t="n">
-        <v>17</v>
+        <v>164</v>
       </c>
       <c r="R291" s="25" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="S291" s="25" t="n">
         <v>725.91</v>
@@ -47803,11 +47125,7 @@
         <v>898.66</v>
       </c>
       <c r="O292" s="25" t="n"/>
-      <c r="P292" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P292" s="25" t="n"/>
       <c r="Q292" s="25" t="n"/>
       <c r="R292" s="25" t="n"/>
       <c r="S292" s="25" t="n"/>
@@ -47967,19 +47285,11 @@
         </is>
       </c>
       <c r="Q293" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="R293" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S293" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T293" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="R293" s="25" t="n"/>
+      <c r="S293" s="25" t="n"/>
+      <c r="T293" s="25" t="n"/>
       <c r="U293" s="25" t="n">
         <v>0</v>
       </c>
@@ -48127,11 +47437,7 @@
         <v>1650.9</v>
       </c>
       <c r="O294" s="25" t="n"/>
-      <c r="P294" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P294" s="25" t="n"/>
       <c r="Q294" s="25" t="n"/>
       <c r="R294" s="25" t="n"/>
       <c r="S294" s="25" t="n"/>
@@ -48283,11 +47589,7 @@
         <v>704</v>
       </c>
       <c r="O295" s="25" t="n"/>
-      <c r="P295" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P295" s="25" t="n"/>
       <c r="Q295" s="25" t="n"/>
       <c r="R295" s="25" t="n"/>
       <c r="S295" s="25" t="n"/>
@@ -48447,7 +47749,7 @@
         </is>
       </c>
       <c r="Q296" s="25" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="R296" s="25" t="n">
         <v>10</v>
@@ -48607,11 +47909,7 @@
         <v>2693.25</v>
       </c>
       <c r="O297" s="25" t="n"/>
-      <c r="P297" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P297" s="25" t="n"/>
       <c r="Q297" s="25" t="n"/>
       <c r="R297" s="25" t="n"/>
       <c r="S297" s="25" t="n"/>
@@ -48763,11 +48061,7 @@
         <v>657.9</v>
       </c>
       <c r="O298" s="25" t="n"/>
-      <c r="P298" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P298" s="25" t="n"/>
       <c r="Q298" s="25" t="n"/>
       <c r="R298" s="25" t="n"/>
       <c r="S298" s="25" t="n"/>
@@ -48912,11 +48206,7 @@
         <v>658.35</v>
       </c>
       <c r="O299" s="25" t="n"/>
-      <c r="P299" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P299" s="25" t="n"/>
       <c r="Q299" s="25" t="n"/>
       <c r="R299" s="25" t="n"/>
       <c r="S299" s="25" t="n"/>
@@ -49056,11 +48346,7 @@
         <v>658.35</v>
       </c>
       <c r="O300" s="25" t="n"/>
-      <c r="P300" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P300" s="25" t="n"/>
       <c r="Q300" s="25" t="n"/>
       <c r="R300" s="25" t="n"/>
       <c r="S300" s="25" t="n"/>
@@ -49200,11 +48486,7 @@
         <v>657.9</v>
       </c>
       <c r="O301" s="25" t="n"/>
-      <c r="P301" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P301" s="25" t="n"/>
       <c r="Q301" s="25" t="n"/>
       <c r="R301" s="25" t="n"/>
       <c r="S301" s="25" t="n"/>
@@ -49349,11 +48631,7 @@
         <v>658.35</v>
       </c>
       <c r="O302" s="25" t="n"/>
-      <c r="P302" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P302" s="25" t="n"/>
       <c r="Q302" s="25" t="n"/>
       <c r="R302" s="25" t="n"/>
       <c r="S302" s="25" t="n"/>
@@ -49493,11 +48771,7 @@
         <v>658.35</v>
       </c>
       <c r="O303" s="25" t="n"/>
-      <c r="P303" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P303" s="25" t="n"/>
       <c r="Q303" s="25" t="n"/>
       <c r="R303" s="25" t="n"/>
       <c r="S303" s="25" t="n"/>
@@ -49645,7 +48919,7 @@
         </is>
       </c>
       <c r="Q304" s="25" t="n">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="R304" s="25" t="n">
         <v>27</v>
@@ -49817,7 +49091,7 @@
         </is>
       </c>
       <c r="Q305" s="25" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="R305" s="25" t="n">
         <v>8</v>
@@ -49985,10 +49259,10 @@
         </is>
       </c>
       <c r="Q306" s="25" t="n">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="R306" s="25" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="S306" s="25" t="n">
         <v>5170.48</v>
@@ -50159,17 +49433,9 @@
       <c r="Q307" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="R307" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S307" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T307" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="R307" s="25" t="n"/>
+      <c r="S307" s="25" t="n"/>
+      <c r="T307" s="25" t="n"/>
       <c r="U307" s="25" t="n">
         <v>0</v>
       </c>
@@ -50325,10 +49591,10 @@
         </is>
       </c>
       <c r="Q308" s="25" t="n">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="R308" s="25" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="S308" s="25" t="n">
         <v>348.16</v>
@@ -50485,11 +49751,7 @@
         <v>2490.01</v>
       </c>
       <c r="O309" s="25" t="n"/>
-      <c r="P309" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P309" s="25" t="n"/>
       <c r="Q309" s="25" t="n"/>
       <c r="R309" s="25" t="n"/>
       <c r="S309" s="25" t="n"/>
@@ -50645,11 +49907,7 @@
         <v>1218.44</v>
       </c>
       <c r="O310" s="25" t="n"/>
-      <c r="P310" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P310" s="25" t="n"/>
       <c r="Q310" s="25" t="n"/>
       <c r="R310" s="25" t="n"/>
       <c r="S310" s="25" t="n"/>
@@ -50805,11 +50063,7 @@
         <v>880</v>
       </c>
       <c r="O311" s="25" t="n"/>
-      <c r="P311" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P311" s="25" t="n"/>
       <c r="Q311" s="25" t="n"/>
       <c r="R311" s="25" t="n"/>
       <c r="S311" s="25" t="n"/>
@@ -50975,17 +50229,9 @@
       <c r="Q312" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="R312" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S312" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T312" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="R312" s="25" t="n"/>
+      <c r="S312" s="25" t="n"/>
+      <c r="T312" s="25" t="n"/>
       <c r="U312" s="25" t="n">
         <v>0</v>
       </c>
@@ -51137,11 +50383,7 @@
         <v>705.02</v>
       </c>
       <c r="O313" s="25" t="n"/>
-      <c r="P313" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P313" s="25" t="n"/>
       <c r="Q313" s="25" t="n"/>
       <c r="R313" s="25" t="n"/>
       <c r="S313" s="25" t="n"/>
@@ -51297,11 +50539,7 @@
         <v>706.23</v>
       </c>
       <c r="O314" s="25" t="n"/>
-      <c r="P314" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P314" s="25" t="n"/>
       <c r="Q314" s="25" t="n"/>
       <c r="R314" s="25" t="n"/>
       <c r="S314" s="25" t="n"/>
@@ -51457,11 +50695,7 @@
         <v>1304.15</v>
       </c>
       <c r="O315" s="25" t="n"/>
-      <c r="P315" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P315" s="25" t="n"/>
       <c r="Q315" s="25" t="n"/>
       <c r="R315" s="25" t="n"/>
       <c r="S315" s="25" t="n"/>
@@ -51621,10 +50855,10 @@
         </is>
       </c>
       <c r="Q316" s="25" t="n">
-        <v>35</v>
+        <v>149</v>
       </c>
       <c r="R316" s="25" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="S316" s="25" t="n">
         <v>1454.54</v>
@@ -51789,10 +51023,10 @@
         </is>
       </c>
       <c r="Q317" s="25" t="n">
-        <v>41</v>
+        <v>117</v>
       </c>
       <c r="R317" s="25" t="n">
-        <v>646.5700000000001</v>
+        <v>16</v>
       </c>
       <c r="S317" s="25" t="n">
         <v>753.1900000000001</v>
@@ -51949,11 +51183,7 @@
         <v>4632.41</v>
       </c>
       <c r="O318" s="25" t="n"/>
-      <c r="P318" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P318" s="25" t="n"/>
       <c r="Q318" s="25" t="n"/>
       <c r="R318" s="25" t="n"/>
       <c r="S318" s="25" t="n"/>
@@ -52109,11 +51339,7 @@
         <v>1593.58</v>
       </c>
       <c r="O319" s="25" t="n"/>
-      <c r="P319" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P319" s="25" t="n"/>
       <c r="Q319" s="25" t="n"/>
       <c r="R319" s="25" t="n"/>
       <c r="S319" s="25" t="n"/>
@@ -52277,7 +51503,7 @@
         </is>
       </c>
       <c r="Q320" s="25" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="R320" s="25" t="n">
         <v>10</v>
@@ -52445,7 +51671,7 @@
         </is>
       </c>
       <c r="Q321" s="25" t="n">
-        <v>17</v>
+        <v>155</v>
       </c>
       <c r="R321" s="25" t="n">
         <v>19</v>
@@ -52613,7 +51839,7 @@
         </is>
       </c>
       <c r="Q322" s="25" t="n">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="R322" s="25" t="n">
         <v>12</v>
@@ -52773,11 +51999,7 @@
         <v>774</v>
       </c>
       <c r="O323" s="25" t="n"/>
-      <c r="P323" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P323" s="25" t="n"/>
       <c r="Q323" s="25" t="n"/>
       <c r="R323" s="25" t="n"/>
       <c r="S323" s="25" t="n"/>
@@ -52937,10 +52159,10 @@
         </is>
       </c>
       <c r="Q324" s="25" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="R324" s="25" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="S324" s="25" t="n">
         <v>4248.73</v>
@@ -53102,11 +52324,7 @@
         <v>670.83</v>
       </c>
       <c r="O325" s="25" t="n"/>
-      <c r="P325" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P325" s="25" t="n"/>
       <c r="Q325" s="25" t="n"/>
       <c r="R325" s="25" t="n"/>
       <c r="S325" s="25" t="n"/>
@@ -53263,11 +52481,7 @@
         <v>2062.63</v>
       </c>
       <c r="O326" s="25" t="n"/>
-      <c r="P326" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P326" s="25" t="n"/>
       <c r="Q326" s="25" t="n"/>
       <c r="R326" s="25" t="n"/>
       <c r="S326" s="25" t="n"/>
@@ -53427,13 +52641,13 @@
         </is>
       </c>
       <c r="Q327" s="25" t="n">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="R327" s="25" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="S327" s="25" t="n">
-        <v>1676.9</v>
+        <v>838.45</v>
       </c>
       <c r="T327" s="25" t="inlineStr">
         <is>
@@ -53587,11 +52801,7 @@
         <v>1568.19</v>
       </c>
       <c r="O328" s="25" t="n"/>
-      <c r="P328" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P328" s="25" t="n"/>
       <c r="Q328" s="25" t="n"/>
       <c r="R328" s="25" t="n"/>
       <c r="S328" s="25" t="n"/>
@@ -53751,19 +52961,17 @@
       <c r="N329" s="25" t="n">
         <v>802.23</v>
       </c>
-      <c r="O329" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="O329" s="25" t="n"/>
       <c r="P329" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
       <c r="Q329" s="25" t="n">
-        <v>9</v>
+        <v>142</v>
       </c>
       <c r="R329" s="25" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="S329" s="25" t="n">
         <v>1674.14</v>
@@ -53928,19 +53136,13 @@
         </is>
       </c>
       <c r="Q330" s="25" t="n">
-        <v>34</v>
+        <v>144</v>
       </c>
       <c r="R330" s="25" t="n">
         <v>33</v>
       </c>
-      <c r="S330" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T330" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="S330" s="25" t="n"/>
+      <c r="T330" s="25" t="n"/>
       <c r="U330" s="25" t="n">
         <v>0</v>
       </c>
@@ -54096,10 +53298,10 @@
         </is>
       </c>
       <c r="Q331" s="25" t="n">
-        <v>5</v>
+        <v>101</v>
       </c>
       <c r="R331" s="25" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S331" s="25" t="n">
         <v>2046.8</v>
@@ -54264,7 +53466,7 @@
         </is>
       </c>
       <c r="Q332" s="25" t="n">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="R332" s="25" t="n">
         <v>25</v>
@@ -54428,11 +53630,7 @@
         <v>690.8</v>
       </c>
       <c r="O333" s="25" t="n"/>
-      <c r="P333" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P333" s="25" t="n"/>
       <c r="Q333" s="25" t="n"/>
       <c r="R333" s="25" t="n"/>
       <c r="S333" s="25" t="n"/>
@@ -54592,10 +53790,10 @@
         </is>
       </c>
       <c r="Q334" s="25" t="n">
-        <v>97</v>
+        <v>487</v>
       </c>
       <c r="R334" s="25" t="n">
-        <v>700.4400000000001</v>
+        <v>85</v>
       </c>
       <c r="S334" s="25" t="n">
         <v>1735.25</v>
@@ -54760,13 +53958,13 @@
         </is>
       </c>
       <c r="Q335" s="25" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="R335" s="25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S335" s="25" t="n">
-        <v>2144.18</v>
+        <v>1072.09</v>
       </c>
       <c r="T335" s="25" t="inlineStr">
         <is>
@@ -54916,13 +54114,13 @@
         </is>
       </c>
       <c r="Q336" s="25" t="n">
-        <v>104</v>
+        <v>365</v>
       </c>
       <c r="R336" s="25" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="S336" s="25" t="n">
-        <v>3354.73</v>
+        <v>2075.22</v>
       </c>
       <c r="T336" s="25" t="inlineStr">
         <is>
@@ -55084,10 +54282,10 @@
         </is>
       </c>
       <c r="Q337" s="25" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="R337" s="25" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="S337" s="25" t="n">
         <v>1560.86</v>
@@ -55248,11 +54446,11 @@
       </c>
       <c r="P338" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="Q338" s="25" t="n">
-        <v>6</v>
+        <v>97</v>
       </c>
       <c r="R338" s="25" t="n">
         <v>28</v>
@@ -55415,14 +54613,20 @@
       <c r="N339" s="25" t="n">
         <v>1256.12</v>
       </c>
-      <c r="O339" s="25" t="n"/>
+      <c r="O339" s="25" t="n">
+        <v>4</v>
+      </c>
       <c r="P339" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="Q339" s="25" t="n"/>
-      <c r="R339" s="25" t="n"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q339" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="R339" s="25" t="n">
+        <v>45</v>
+      </c>
       <c r="S339" s="25" t="n"/>
       <c r="T339" s="25" t="n"/>
       <c r="U339" s="25" t="n">
@@ -55560,11 +54764,7 @@
         <v>2931.2</v>
       </c>
       <c r="O340" s="25" t="n"/>
-      <c r="P340" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P340" s="25" t="n"/>
       <c r="Q340" s="25" t="n"/>
       <c r="R340" s="25" t="n"/>
       <c r="S340" s="25" t="n"/>
@@ -55716,11 +54916,7 @@
         <v>11358.43</v>
       </c>
       <c r="O341" s="25" t="n"/>
-      <c r="P341" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P341" s="25" t="n"/>
       <c r="Q341" s="25" t="n"/>
       <c r="R341" s="25" t="n"/>
       <c r="S341" s="25" t="n"/>
@@ -55864,11 +55060,7 @@
         <v>2350.33</v>
       </c>
       <c r="O342" s="25" t="n"/>
-      <c r="P342" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P342" s="25" t="n"/>
       <c r="Q342" s="25" t="n"/>
       <c r="R342" s="25" t="n"/>
       <c r="S342" s="25" t="n"/>
@@ -56028,13 +55220,13 @@
         </is>
       </c>
       <c r="Q343" s="25" t="n">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="R343" s="25" t="n">
         <v>29</v>
       </c>
       <c r="S343" s="25" t="n">
-        <v>4475.28</v>
+        <v>2237.64</v>
       </c>
       <c r="T343" s="25" t="inlineStr">
         <is>
@@ -56196,10 +55388,10 @@
         </is>
       </c>
       <c r="Q344" s="25" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="R344" s="25" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S344" s="25" t="n">
         <v>881.22</v>
@@ -56360,11 +55552,7 @@
         <v>892.7</v>
       </c>
       <c r="O345" s="25" t="n"/>
-      <c r="P345" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P345" s="25" t="n"/>
       <c r="Q345" s="25" t="n"/>
       <c r="R345" s="25" t="n"/>
       <c r="S345" s="25" t="n"/>
@@ -56524,19 +55712,13 @@
         </is>
       </c>
       <c r="Q346" s="25" t="n">
-        <v>10</v>
+        <v>179</v>
       </c>
       <c r="R346" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S346" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T346" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="S346" s="25" t="n"/>
+      <c r="T346" s="25" t="n"/>
       <c r="U346" s="25" t="n">
         <v>0</v>
       </c>
@@ -56692,10 +55874,10 @@
         </is>
       </c>
       <c r="Q347" s="25" t="n">
-        <v>3</v>
+        <v>130</v>
       </c>
       <c r="R347" s="25" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="S347" s="25" t="n">
         <v>1163.03</v>
@@ -56852,11 +56034,7 @@
         <v>675.8</v>
       </c>
       <c r="O348" s="25" t="n"/>
-      <c r="P348" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P348" s="25" t="n"/>
       <c r="Q348" s="25" t="n"/>
       <c r="R348" s="25" t="n"/>
       <c r="S348" s="25" t="n"/>
@@ -57004,10 +56182,10 @@
         </is>
       </c>
       <c r="Q349" s="25" t="n">
-        <v>6</v>
+        <v>102</v>
       </c>
       <c r="R349" s="25" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="S349" s="25" t="n">
         <v>1432.52</v>
@@ -57164,11 +56342,7 @@
         <v>2335.96</v>
       </c>
       <c r="O350" s="25" t="n"/>
-      <c r="P350" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P350" s="25" t="n"/>
       <c r="Q350" s="25" t="n"/>
       <c r="R350" s="25" t="n"/>
       <c r="S350" s="25" t="n"/>
@@ -57320,11 +56494,7 @@
         <v>1754.42</v>
       </c>
       <c r="O351" s="25" t="n"/>
-      <c r="P351" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P351" s="25" t="n"/>
       <c r="Q351" s="25" t="n"/>
       <c r="R351" s="25" t="n"/>
       <c r="S351" s="25" t="n"/>
@@ -57480,11 +56650,7 @@
         <v>820.8</v>
       </c>
       <c r="O352" s="25" t="n"/>
-      <c r="P352" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P352" s="25" t="n"/>
       <c r="Q352" s="25" t="n"/>
       <c r="R352" s="25" t="n"/>
       <c r="S352" s="25" t="n"/>
@@ -57644,7 +56810,7 @@
         </is>
       </c>
       <c r="Q353" s="25" t="n">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="R353" s="25" t="n">
         <v>23</v>
@@ -57816,19 +56982,11 @@
         </is>
       </c>
       <c r="Q354" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R354" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S354" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T354" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="R354" s="25" t="n"/>
+      <c r="S354" s="25" t="n"/>
+      <c r="T354" s="25" t="n"/>
       <c r="U354" s="25" t="n">
         <v>0</v>
       </c>
@@ -57984,7 +57142,7 @@
         </is>
       </c>
       <c r="Q355" s="25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R355" s="25" t="n">
         <v>1</v>
@@ -58144,11 +57302,7 @@
         <v>1012.6</v>
       </c>
       <c r="O356" s="25" t="n"/>
-      <c r="P356" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P356" s="25" t="n"/>
       <c r="Q356" s="25" t="n"/>
       <c r="R356" s="25" t="n"/>
       <c r="S356" s="25" t="n"/>
@@ -58288,25 +57442,11 @@
         <v>1452.42</v>
       </c>
       <c r="O357" s="25" t="n"/>
-      <c r="P357" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="Q357" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="R357" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S357" s="25" t="n">
-        <v>24</v>
-      </c>
-      <c r="T357" s="25" t="inlineStr">
-        <is>
-          <t>COMPRA B2B</t>
-        </is>
-      </c>
+      <c r="P357" s="25" t="n"/>
+      <c r="Q357" s="25" t="n"/>
+      <c r="R357" s="25" t="n"/>
+      <c r="S357" s="25" t="n"/>
+      <c r="T357" s="25" t="n"/>
       <c r="U357" s="25" t="n">
         <v>0</v>
       </c>
@@ -58441,26 +57581,20 @@
       <c r="N358" s="25" t="n">
         <v>4460.93</v>
       </c>
-      <c r="O358" s="25" t="n"/>
+      <c r="O358" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="P358" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
       <c r="Q358" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="R358" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S358" s="25" t="n">
-        <v>24</v>
-      </c>
-      <c r="T358" s="25" t="inlineStr">
-        <is>
-          <t>COMPRA B2B</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="R358" s="25" t="n"/>
+      <c r="S358" s="25" t="n"/>
+      <c r="T358" s="25" t="n"/>
       <c r="U358" s="25" t="n">
         <v>0</v>
       </c>
@@ -58596,11 +57730,7 @@
         <v>1453.67</v>
       </c>
       <c r="O359" s="25" t="n"/>
-      <c r="P359" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P359" s="25" t="n"/>
       <c r="Q359" s="25" t="n"/>
       <c r="R359" s="25" t="n"/>
       <c r="S359" s="25" t="n"/>
@@ -58752,11 +57882,7 @@
         <v>1392.8</v>
       </c>
       <c r="O360" s="25" t="n"/>
-      <c r="P360" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P360" s="25" t="n"/>
       <c r="Q360" s="25" t="n"/>
       <c r="R360" s="25" t="n"/>
       <c r="S360" s="25" t="n"/>
@@ -58908,11 +58034,7 @@
         <v>1783.27</v>
       </c>
       <c r="O361" s="25" t="n"/>
-      <c r="P361" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P361" s="25" t="n"/>
       <c r="Q361" s="25" t="n"/>
       <c r="R361" s="25" t="n"/>
       <c r="S361" s="25" t="n"/>
@@ -59076,13 +58198,13 @@
         </is>
       </c>
       <c r="Q362" s="25" t="n">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="R362" s="25" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S362" s="25" t="n">
-        <v>5988.4</v>
+        <v>4272.1</v>
       </c>
       <c r="T362" s="25" t="inlineStr">
         <is>
@@ -59240,11 +58362,7 @@
         <v>1138.05</v>
       </c>
       <c r="O363" s="25" t="n"/>
-      <c r="P363" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P363" s="25" t="n"/>
       <c r="Q363" s="25" t="n"/>
       <c r="R363" s="25" t="n"/>
       <c r="S363" s="25" t="n"/>
@@ -59404,10 +58522,10 @@
         </is>
       </c>
       <c r="Q364" s="25" t="n">
-        <v>7</v>
+        <v>95</v>
       </c>
       <c r="R364" s="25" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="S364" s="25" t="n">
         <v>4270.04</v>
@@ -59564,7 +58682,7 @@
         <v>681.47</v>
       </c>
       <c r="O365" s="25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P365" s="25" t="inlineStr">
         <is>
@@ -59572,10 +58690,10 @@
         </is>
       </c>
       <c r="Q365" s="25" t="n">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="R365" s="25" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="S365" s="25" t="n">
         <v>1370.93</v>
@@ -59732,11 +58850,7 @@
         <v>853.74</v>
       </c>
       <c r="O366" s="25" t="n"/>
-      <c r="P366" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P366" s="25" t="n"/>
       <c r="Q366" s="25" t="n"/>
       <c r="R366" s="25" t="n"/>
       <c r="S366" s="25" t="n"/>
@@ -59888,11 +59002,7 @@
         <v>2505.43</v>
       </c>
       <c r="O367" s="25" t="n"/>
-      <c r="P367" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P367" s="25" t="n"/>
       <c r="Q367" s="25" t="n"/>
       <c r="R367" s="25" t="n"/>
       <c r="S367" s="25" t="n"/>
@@ -60044,11 +59154,7 @@
         <v>2525.84</v>
       </c>
       <c r="O368" s="25" t="n"/>
-      <c r="P368" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P368" s="25" t="n"/>
       <c r="Q368" s="25" t="n"/>
       <c r="R368" s="25" t="n"/>
       <c r="S368" s="25" t="n"/>
@@ -60200,11 +59306,7 @@
         <v>3863.5</v>
       </c>
       <c r="O369" s="25" t="n"/>
-      <c r="P369" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P369" s="25" t="n"/>
       <c r="Q369" s="25" t="n"/>
       <c r="R369" s="25" t="n"/>
       <c r="S369" s="25" t="n"/>
@@ -60356,11 +59458,7 @@
         <v>3343</v>
       </c>
       <c r="O370" s="25" t="n"/>
-      <c r="P370" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P370" s="25" t="n"/>
       <c r="Q370" s="25" t="n"/>
       <c r="R370" s="25" t="n"/>
       <c r="S370" s="25" t="n"/>
@@ -60512,11 +59610,7 @@
         <v>1188.14</v>
       </c>
       <c r="O371" s="25" t="n"/>
-      <c r="P371" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P371" s="25" t="n"/>
       <c r="Q371" s="25" t="n"/>
       <c r="R371" s="25" t="n"/>
       <c r="S371" s="25" t="n"/>
@@ -60668,11 +59762,7 @@
         <v>704.65</v>
       </c>
       <c r="O372" s="25" t="n"/>
-      <c r="P372" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P372" s="25" t="n"/>
       <c r="Q372" s="25" t="n"/>
       <c r="R372" s="25" t="n"/>
       <c r="S372" s="25" t="n"/>
@@ -60824,7 +59914,7 @@
         <v>682.33</v>
       </c>
       <c r="O373" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P373" s="25" t="inlineStr">
         <is>
@@ -60832,19 +59922,13 @@
         </is>
       </c>
       <c r="Q373" s="25" t="n">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="R373" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S373" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T373" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="S373" s="25" t="n"/>
+      <c r="T373" s="25" t="n"/>
       <c r="U373" s="25" t="n">
         <v>0</v>
       </c>
@@ -60992,11 +60076,7 @@
         <v>5301.79</v>
       </c>
       <c r="O374" s="25" t="n"/>
-      <c r="P374" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P374" s="25" t="n"/>
       <c r="Q374" s="25" t="n"/>
       <c r="R374" s="25" t="n"/>
       <c r="S374" s="25" t="n"/>
@@ -61144,7 +60224,7 @@
         </is>
       </c>
       <c r="Q375" s="25" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="R375" s="25" t="n">
         <v>19</v>
@@ -61312,10 +60392,10 @@
         </is>
       </c>
       <c r="Q376" s="25" t="n">
-        <v>5</v>
+        <v>157</v>
       </c>
       <c r="R376" s="25" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S376" s="25" t="n">
         <v>773.6900000000001</v>
@@ -61480,7 +60560,7 @@
         </is>
       </c>
       <c r="Q377" s="25" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="R377" s="25" t="n">
         <v>28</v>
@@ -61648,10 +60728,10 @@
         </is>
       </c>
       <c r="Q378" s="25" t="n">
-        <v>5</v>
+        <v>301</v>
       </c>
       <c r="R378" s="25" t="n">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="S378" s="25" t="n">
         <v>3710.21</v>
@@ -61808,11 +60888,7 @@
         <v>1206.12</v>
       </c>
       <c r="O379" s="25" t="n"/>
-      <c r="P379" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P379" s="25" t="n"/>
       <c r="Q379" s="25" t="n"/>
       <c r="R379" s="25" t="n"/>
       <c r="S379" s="25" t="n"/>
@@ -61976,10 +61052,10 @@
         </is>
       </c>
       <c r="Q380" s="25" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="R380" s="25" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S380" s="25" t="n">
         <v>653.75</v>
@@ -62144,7 +61220,7 @@
         </is>
       </c>
       <c r="Q381" s="25" t="n">
-        <v>7</v>
+        <v>101</v>
       </c>
       <c r="R381" s="25" t="n">
         <v>12</v>
@@ -62308,11 +61384,7 @@
         <v>1218.44</v>
       </c>
       <c r="O382" s="25" t="n"/>
-      <c r="P382" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P382" s="25" t="n"/>
       <c r="Q382" s="25" t="n"/>
       <c r="R382" s="25" t="n"/>
       <c r="S382" s="25" t="n"/>
@@ -62468,11 +61540,7 @@
         <v>1076.41</v>
       </c>
       <c r="O383" s="25" t="n"/>
-      <c r="P383" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P383" s="25" t="n"/>
       <c r="Q383" s="25" t="n"/>
       <c r="R383" s="25" t="n"/>
       <c r="S383" s="25" t="n"/>
@@ -62628,11 +61696,7 @@
         <v>1213.9</v>
       </c>
       <c r="O384" s="25" t="n"/>
-      <c r="P384" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P384" s="25" t="n"/>
       <c r="Q384" s="25" t="n"/>
       <c r="R384" s="25" t="n"/>
       <c r="S384" s="25" t="n"/>
@@ -62784,11 +61848,7 @@
         <v>3300</v>
       </c>
       <c r="O385" s="25" t="n"/>
-      <c r="P385" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P385" s="25" t="n"/>
       <c r="Q385" s="25" t="n"/>
       <c r="R385" s="25" t="n"/>
       <c r="S385" s="25" t="n"/>
@@ -62945,11 +62005,7 @@
         <v>1745.52</v>
       </c>
       <c r="O386" s="25" t="n"/>
-      <c r="P386" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P386" s="25" t="n"/>
       <c r="Q386" s="25" t="n"/>
       <c r="R386" s="25" t="n"/>
       <c r="S386" s="25" t="n"/>
@@ -63109,10 +62165,10 @@
         </is>
       </c>
       <c r="Q387" s="25" t="n">
-        <v>4</v>
+        <v>193</v>
       </c>
       <c r="R387" s="25" t="n">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="S387" s="25" t="n">
         <v>3026.55</v>
@@ -63277,10 +62333,10 @@
         </is>
       </c>
       <c r="Q388" s="25" t="n">
-        <v>5</v>
+        <v>241</v>
       </c>
       <c r="R388" s="25" t="n">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="S388" s="25" t="n">
         <v>5909.89</v>
@@ -63449,10 +62505,10 @@
         </is>
       </c>
       <c r="Q389" s="25" t="n">
-        <v>3</v>
+        <v>153</v>
       </c>
       <c r="R389" s="25" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="S389" s="25" t="n">
         <v>4976.02</v>
@@ -63621,10 +62677,10 @@
         </is>
       </c>
       <c r="Q390" s="25" t="n">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="R390" s="25" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="S390" s="25" t="n">
         <v>4925.21</v>
@@ -63793,7 +62849,7 @@
         </is>
       </c>
       <c r="Q391" s="25" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="R391" s="25" t="n">
         <v>22</v>
@@ -63953,11 +63009,7 @@
         <v>650.3</v>
       </c>
       <c r="O392" s="25" t="n"/>
-      <c r="P392" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P392" s="25" t="n"/>
       <c r="Q392" s="25" t="n"/>
       <c r="R392" s="25" t="n"/>
       <c r="S392" s="25" t="n"/>
@@ -64122,10 +63174,10 @@
         </is>
       </c>
       <c r="Q393" s="25" t="n">
-        <v>6</v>
+        <v>107</v>
       </c>
       <c r="R393" s="25" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="S393" s="25" t="n">
         <v>2795.54</v>
@@ -64290,10 +63342,10 @@
         </is>
       </c>
       <c r="Q394" s="25" t="n">
-        <v>14</v>
+        <v>148</v>
       </c>
       <c r="R394" s="25" t="n">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="S394" s="25" t="n">
         <v>6049.11</v>
@@ -64458,10 +63510,10 @@
         </is>
       </c>
       <c r="Q395" s="25" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R395" s="25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S395" s="25" t="n">
         <v>1025.88</v>
@@ -64626,19 +63678,11 @@
         </is>
       </c>
       <c r="Q396" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="R396" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S396" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T396" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="R396" s="25" t="n"/>
+      <c r="S396" s="25" t="n"/>
+      <c r="T396" s="25" t="n"/>
       <c r="U396" s="25" t="n">
         <v>0</v>
       </c>
@@ -64774,11 +63818,7 @@
         <v>10200.37</v>
       </c>
       <c r="O397" s="25" t="n"/>
-      <c r="P397" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P397" s="25" t="n"/>
       <c r="Q397" s="25" t="n"/>
       <c r="R397" s="25" t="n"/>
       <c r="S397" s="25" t="n"/>
@@ -64938,7 +63978,7 @@
         </is>
       </c>
       <c r="Q398" s="25" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="R398" s="25" t="n">
         <v>26</v>
@@ -65098,11 +64138,7 @@
         <v>699.37</v>
       </c>
       <c r="O399" s="25" t="n"/>
-      <c r="P399" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P399" s="25" t="n"/>
       <c r="Q399" s="25" t="n"/>
       <c r="R399" s="25" t="n"/>
       <c r="S399" s="25" t="n"/>
@@ -65254,11 +64290,7 @@
         <v>768</v>
       </c>
       <c r="O400" s="25" t="n"/>
-      <c r="P400" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P400" s="25" t="n"/>
       <c r="Q400" s="25" t="n"/>
       <c r="R400" s="25" t="n"/>
       <c r="S400" s="25" t="n"/>
@@ -65422,19 +64454,11 @@
         </is>
       </c>
       <c r="Q401" s="25" t="n">
-        <v>11</v>
-      </c>
-      <c r="R401" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S401" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T401" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="R401" s="25" t="n"/>
+      <c r="S401" s="25" t="n"/>
+      <c r="T401" s="25" t="n"/>
       <c r="U401" s="25" t="n">
         <v>0</v>
       </c>
@@ -65586,11 +64610,7 @@
         <v>1213.9</v>
       </c>
       <c r="O402" s="25" t="n"/>
-      <c r="P402" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P402" s="25" t="n"/>
       <c r="Q402" s="25" t="n"/>
       <c r="R402" s="25" t="n"/>
       <c r="S402" s="25" t="n"/>
@@ -65738,7 +64758,7 @@
         </is>
       </c>
       <c r="Q403" s="25" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="R403" s="25" t="n">
         <v>46</v>
@@ -65897,13 +64917,17 @@
       <c r="N404" s="25" t="n">
         <v>1958.68</v>
       </c>
-      <c r="O404" s="25" t="n"/>
+      <c r="O404" s="25" t="n">
+        <v>2</v>
+      </c>
       <c r="P404" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="Q404" s="25" t="n"/>
+      <c r="Q404" s="25" t="n">
+        <v>2</v>
+      </c>
       <c r="R404" s="25" t="n"/>
       <c r="S404" s="25" t="n"/>
       <c r="T404" s="25" t="n"/>
@@ -66054,11 +65078,7 @@
         <v>3353.25</v>
       </c>
       <c r="O405" s="25" t="n"/>
-      <c r="P405" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P405" s="25" t="n"/>
       <c r="Q405" s="25" t="n"/>
       <c r="R405" s="25" t="n"/>
       <c r="S405" s="25" t="n"/>
@@ -66206,10 +65226,10 @@
         </is>
       </c>
       <c r="Q406" s="25" t="n">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="R406" s="25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S406" s="25" t="n">
         <v>3353.25</v>
@@ -66370,11 +65390,7 @@
         <v>660.46</v>
       </c>
       <c r="O407" s="25" t="n"/>
-      <c r="P407" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P407" s="25" t="n"/>
       <c r="Q407" s="25" t="n"/>
       <c r="R407" s="25" t="n"/>
       <c r="S407" s="25" t="n"/>
@@ -66539,7 +65555,7 @@
         </is>
       </c>
       <c r="Q408" s="25" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="R408" s="25" t="n">
         <v>4</v>
@@ -66707,10 +65723,10 @@
         </is>
       </c>
       <c r="Q409" s="25" t="n">
-        <v>14</v>
+        <v>543</v>
       </c>
       <c r="R409" s="25" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="S409" s="25" t="n">
         <v>3760.82</v>
@@ -66871,11 +65887,7 @@
         <v>1021.87</v>
       </c>
       <c r="O410" s="25" t="n"/>
-      <c r="P410" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P410" s="25" t="n"/>
       <c r="Q410" s="25" t="n"/>
       <c r="R410" s="25" t="n"/>
       <c r="S410" s="25" t="n"/>
@@ -67027,11 +66039,7 @@
         <v>810.36</v>
       </c>
       <c r="O411" s="25" t="n"/>
-      <c r="P411" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P411" s="25" t="n"/>
       <c r="Q411" s="25" t="n"/>
       <c r="R411" s="25" t="n"/>
       <c r="S411" s="25" t="n"/>
@@ -67171,11 +66179,7 @@
         <v>810.36</v>
       </c>
       <c r="O412" s="25" t="n"/>
-      <c r="P412" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P412" s="25" t="n"/>
       <c r="Q412" s="25" t="n"/>
       <c r="R412" s="25" t="n"/>
       <c r="S412" s="25" t="n"/>
@@ -67315,11 +66319,7 @@
         <v>810.36</v>
       </c>
       <c r="O413" s="25" t="n"/>
-      <c r="P413" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P413" s="25" t="n"/>
       <c r="Q413" s="25" t="n"/>
       <c r="R413" s="25" t="n"/>
       <c r="S413" s="25" t="n"/>
@@ -67467,7 +66467,7 @@
         </is>
       </c>
       <c r="Q414" s="25" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="R414" s="25" t="n">
         <v>33</v>
@@ -67639,7 +66639,7 @@
         </is>
       </c>
       <c r="Q415" s="25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R415" s="25" t="n">
         <v>6</v>
@@ -67807,19 +66807,13 @@
         </is>
       </c>
       <c r="Q416" s="25" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="R416" s="25" t="n">
         <v>31</v>
       </c>
-      <c r="S416" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T416" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="S416" s="25" t="n"/>
+      <c r="T416" s="25" t="n"/>
       <c r="U416" s="25" t="n">
         <v>1662.66</v>
       </c>
@@ -67981,17 +66975,9 @@
       <c r="Q417" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="R417" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S417" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T417" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="R417" s="25" t="n"/>
+      <c r="S417" s="25" t="n"/>
+      <c r="T417" s="25" t="n"/>
       <c r="U417" s="25" t="n">
         <v>0</v>
       </c>
@@ -68143,7 +67129,7 @@
         <v>452.27</v>
       </c>
       <c r="O418" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P418" s="25" t="inlineStr">
         <is>
@@ -68151,10 +67137,10 @@
         </is>
       </c>
       <c r="Q418" s="25" t="n">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="R418" s="25" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="S418" s="25" t="n">
         <v>2933.8</v>
@@ -68314,13 +67300,17 @@
       <c r="N419" s="25" t="n">
         <v>1233.66</v>
       </c>
-      <c r="O419" s="25" t="n"/>
+      <c r="O419" s="25" t="n">
+        <v>3</v>
+      </c>
       <c r="P419" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="Q419" s="25" t="n"/>
+      <c r="Q419" s="25" t="n">
+        <v>33</v>
+      </c>
       <c r="R419" s="25" t="n"/>
       <c r="S419" s="25" t="n"/>
       <c r="T419" s="25" t="n"/>
@@ -68479,7 +67469,7 @@
         </is>
       </c>
       <c r="Q420" s="25" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="R420" s="25" t="n">
         <v>9</v>
@@ -68647,19 +67637,11 @@
         </is>
       </c>
       <c r="Q421" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="R421" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S421" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T421" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="R421" s="25" t="n"/>
+      <c r="S421" s="25" t="n"/>
+      <c r="T421" s="25" t="n"/>
       <c r="U421" s="25" t="n">
         <v>0</v>
       </c>
@@ -68807,11 +67789,7 @@
         <v>275.29</v>
       </c>
       <c r="O422" s="25" t="n"/>
-      <c r="P422" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P422" s="25" t="n"/>
       <c r="Q422" s="25" t="n"/>
       <c r="R422" s="25" t="n"/>
       <c r="S422" s="25" t="n"/>
@@ -68971,7 +67949,7 @@
         </is>
       </c>
       <c r="Q423" s="25" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="R423" s="25" t="n">
         <v>23</v>
@@ -69139,19 +68117,13 @@
         </is>
       </c>
       <c r="Q424" s="25" t="n">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="R424" s="25" t="n">
         <v>34</v>
       </c>
-      <c r="S424" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T424" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="S424" s="25" t="n"/>
+      <c r="T424" s="25" t="n"/>
       <c r="U424" s="25" t="n">
         <v>0</v>
       </c>
@@ -69299,7 +68271,7 @@
         <v>936.23</v>
       </c>
       <c r="O425" s="25" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P425" s="25" t="inlineStr">
         <is>
@@ -69307,10 +68279,10 @@
         </is>
       </c>
       <c r="Q425" s="25" t="n">
+        <v>120</v>
+      </c>
+      <c r="R425" s="25" t="n">
         <v>20</v>
-      </c>
-      <c r="R425" s="25" t="n">
-        <v>0</v>
       </c>
       <c r="S425" s="25" t="n">
         <v>2781.62</v>
@@ -69467,11 +68439,7 @@
         <v>1792.87</v>
       </c>
       <c r="O426" s="25" t="n"/>
-      <c r="P426" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P426" s="25" t="n"/>
       <c r="Q426" s="25" t="n"/>
       <c r="R426" s="25" t="n"/>
       <c r="S426" s="25" t="n"/>
@@ -69636,19 +68604,13 @@
         </is>
       </c>
       <c r="Q427" s="25" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R427" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="S427" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T427" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="S427" s="25" t="n"/>
+      <c r="T427" s="25" t="n"/>
       <c r="U427" s="25" t="n">
         <v>0</v>
       </c>
@@ -69796,11 +68758,7 @@
         <v>4230.69</v>
       </c>
       <c r="O428" s="25" t="n"/>
-      <c r="P428" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P428" s="25" t="n"/>
       <c r="Q428" s="25" t="n"/>
       <c r="R428" s="25" t="n"/>
       <c r="S428" s="25" t="n"/>
@@ -69956,11 +68914,7 @@
         <v>1249.9</v>
       </c>
       <c r="O429" s="25" t="n"/>
-      <c r="P429" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P429" s="25" t="n"/>
       <c r="Q429" s="25" t="n"/>
       <c r="R429" s="25" t="n"/>
       <c r="S429" s="25" t="n"/>
@@ -70113,10 +69067,10 @@
         </is>
       </c>
       <c r="Q430" s="25" t="n">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="R430" s="25" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="S430" s="25" t="n">
         <v>1574.78</v>
@@ -70281,7 +69235,7 @@
         </is>
       </c>
       <c r="Q431" s="25" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="R431" s="25" t="n">
         <v>25</v>
@@ -70449,10 +69403,10 @@
         </is>
       </c>
       <c r="Q432" s="25" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="R432" s="25" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="S432" s="25" t="n">
         <v>1574.78</v>
@@ -70617,13 +69571,13 @@
         </is>
       </c>
       <c r="Q433" s="25" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R433" s="25" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="S433" s="25" t="n">
-        <v>3353.1</v>
+        <v>1676.55</v>
       </c>
       <c r="T433" s="25" t="inlineStr">
         <is>
@@ -70781,11 +69735,7 @@
         <v>1213.9</v>
       </c>
       <c r="O434" s="25" t="n"/>
-      <c r="P434" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P434" s="25" t="n"/>
       <c r="Q434" s="25" t="n"/>
       <c r="R434" s="25" t="n"/>
       <c r="S434" s="25" t="n"/>
@@ -70929,11 +69879,7 @@
         <v>1218.44</v>
       </c>
       <c r="O435" s="25" t="n"/>
-      <c r="P435" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P435" s="25" t="n"/>
       <c r="Q435" s="25" t="n"/>
       <c r="R435" s="25" t="n"/>
       <c r="S435" s="25" t="n"/>
@@ -71085,11 +70031,7 @@
         <v>5482.84</v>
       </c>
       <c r="O436" s="25" t="n"/>
-      <c r="P436" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P436" s="25" t="n"/>
       <c r="Q436" s="25" t="n"/>
       <c r="R436" s="25" t="n"/>
       <c r="S436" s="25" t="n"/>
@@ -71245,11 +70187,7 @@
         <v>1380.17</v>
       </c>
       <c r="O437" s="25" t="n"/>
-      <c r="P437" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P437" s="25" t="n"/>
       <c r="Q437" s="25" t="n"/>
       <c r="R437" s="25" t="n"/>
       <c r="S437" s="25" t="n"/>
@@ -71401,11 +70339,7 @@
         <v>818.67</v>
       </c>
       <c r="O438" s="25" t="n"/>
-      <c r="P438" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P438" s="25" t="n"/>
       <c r="Q438" s="25" t="n"/>
       <c r="R438" s="25" t="n"/>
       <c r="S438" s="25" t="n"/>
@@ -71570,19 +70504,13 @@
         </is>
       </c>
       <c r="Q439" s="25" t="n">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="R439" s="25" t="n">
         <v>61</v>
       </c>
-      <c r="S439" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T439" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="S439" s="25" t="n"/>
+      <c r="T439" s="25" t="n"/>
       <c r="U439" s="25" t="n">
         <v>0</v>
       </c>
@@ -71730,11 +70658,7 @@
         <v>658.5599999999999</v>
       </c>
       <c r="O440" s="25" t="n"/>
-      <c r="P440" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P440" s="25" t="n"/>
       <c r="Q440" s="25" t="n"/>
       <c r="R440" s="25" t="n"/>
       <c r="S440" s="25" t="n"/>
@@ -71894,7 +70818,7 @@
         </is>
       </c>
       <c r="Q441" s="25" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R441" s="25" t="n">
         <v>1</v>
@@ -72058,11 +70982,7 @@
         <v>1099.98</v>
       </c>
       <c r="O442" s="25" t="n"/>
-      <c r="P442" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P442" s="25" t="n"/>
       <c r="Q442" s="25" t="n"/>
       <c r="R442" s="25" t="n"/>
       <c r="S442" s="25" t="n"/>
@@ -72214,11 +71134,7 @@
         <v>2177.3</v>
       </c>
       <c r="O443" s="25" t="n"/>
-      <c r="P443" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P443" s="25" t="n"/>
       <c r="Q443" s="25" t="n"/>
       <c r="R443" s="25" t="n"/>
       <c r="S443" s="25" t="n"/>
@@ -72370,11 +71286,7 @@
         <v>2534.4</v>
       </c>
       <c r="O444" s="25" t="n"/>
-      <c r="P444" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P444" s="25" t="n"/>
       <c r="Q444" s="25" t="n"/>
       <c r="R444" s="25" t="n"/>
       <c r="S444" s="25" t="n"/>
@@ -72534,7 +71446,7 @@
         </is>
       </c>
       <c r="Q445" s="25" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="R445" s="25" t="n">
         <v>6</v>
@@ -72702,19 +71614,11 @@
         </is>
       </c>
       <c r="Q446" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="R446" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S446" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T446" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="R446" s="25" t="n"/>
+      <c r="S446" s="25" t="n"/>
+      <c r="T446" s="25" t="n"/>
       <c r="U446" s="25" t="n">
         <v>0</v>
       </c>
@@ -72866,11 +71770,7 @@
         <v>1571</v>
       </c>
       <c r="O447" s="25" t="n"/>
-      <c r="P447" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P447" s="25" t="n"/>
       <c r="Q447" s="25" t="n"/>
       <c r="R447" s="25" t="n"/>
       <c r="S447" s="25" t="n"/>
@@ -73022,7 +71922,7 @@
         <v>998.4</v>
       </c>
       <c r="O448" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P448" s="25" t="inlineStr">
         <is>
@@ -73030,10 +71930,10 @@
         </is>
       </c>
       <c r="Q448" s="25" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="R448" s="25" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="S448" s="25" t="n">
         <v>998.4</v>
@@ -73190,11 +72090,7 @@
         <v>7124.37</v>
       </c>
       <c r="O449" s="25" t="n"/>
-      <c r="P449" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P449" s="25" t="n"/>
       <c r="Q449" s="25" t="n"/>
       <c r="R449" s="25" t="n"/>
       <c r="S449" s="25" t="n"/>
@@ -73346,11 +72242,7 @@
         <v>2180.46</v>
       </c>
       <c r="O450" s="25" t="n"/>
-      <c r="P450" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P450" s="25" t="n"/>
       <c r="Q450" s="25" t="n"/>
       <c r="R450" s="25" t="n"/>
       <c r="S450" s="25" t="n"/>
@@ -73502,11 +72394,7 @@
         <v>27788.43</v>
       </c>
       <c r="O451" s="25" t="n"/>
-      <c r="P451" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P451" s="25" t="n"/>
       <c r="Q451" s="25" t="n"/>
       <c r="R451" s="25" t="n"/>
       <c r="S451" s="25" t="n"/>
@@ -73666,13 +72554,13 @@
         </is>
       </c>
       <c r="Q452" s="25" t="n">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="R452" s="25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S452" s="25" t="n">
-        <v>26062.8</v>
+        <v>19216.8</v>
       </c>
       <c r="T452" s="25" t="inlineStr">
         <is>
@@ -73834,7 +72722,7 @@
         </is>
       </c>
       <c r="Q453" s="25" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R453" s="25" t="n">
         <v>3</v>
@@ -73994,11 +72882,7 @@
         <v>6041.2</v>
       </c>
       <c r="O454" s="25" t="n"/>
-      <c r="P454" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P454" s="25" t="n"/>
       <c r="Q454" s="25" t="n"/>
       <c r="R454" s="25" t="n"/>
       <c r="S454" s="25" t="n"/>
@@ -74158,19 +73042,13 @@
         </is>
       </c>
       <c r="Q455" s="25" t="n">
-        <v>11</v>
+        <v>198</v>
       </c>
       <c r="R455" s="25" t="n">
         <v>54</v>
       </c>
-      <c r="S455" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T455" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="S455" s="25" t="n"/>
+      <c r="T455" s="25" t="n"/>
       <c r="U455" s="25" t="n">
         <v>0</v>
       </c>
@@ -74326,7 +73204,7 @@
         </is>
       </c>
       <c r="Q456" s="25" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="R456" s="25" t="n">
         <v>12</v>
@@ -74486,11 +73364,7 @@
         <v>661.5700000000001</v>
       </c>
       <c r="O457" s="25" t="n"/>
-      <c r="P457" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P457" s="25" t="n"/>
       <c r="Q457" s="25" t="n"/>
       <c r="R457" s="25" t="n"/>
       <c r="S457" s="25" t="n"/>
@@ -74642,11 +73516,7 @@
         <v>2904.78</v>
       </c>
       <c r="O458" s="25" t="n"/>
-      <c r="P458" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P458" s="25" t="n"/>
       <c r="Q458" s="25" t="n"/>
       <c r="R458" s="25" t="n"/>
       <c r="S458" s="25" t="n"/>
@@ -74806,7 +73676,7 @@
         </is>
       </c>
       <c r="Q459" s="25" t="n">
-        <v>4</v>
+        <v>125</v>
       </c>
       <c r="R459" s="25" t="n">
         <v>33</v>
@@ -74965,28 +73835,12 @@
       <c r="N460" s="25" t="n">
         <v>1576.32</v>
       </c>
-      <c r="O460" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="P460" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="Q460" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R460" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S460" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T460" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="O460" s="25" t="n"/>
+      <c r="P460" s="25" t="n"/>
+      <c r="Q460" s="25" t="n"/>
+      <c r="R460" s="25" t="n"/>
+      <c r="S460" s="25" t="n"/>
+      <c r="T460" s="25" t="n"/>
       <c r="U460" s="25" t="n">
         <v>0</v>
       </c>
@@ -75134,11 +73988,7 @@
         <v>1558.74</v>
       </c>
       <c r="O461" s="25" t="n"/>
-      <c r="P461" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P461" s="25" t="n"/>
       <c r="Q461" s="25" t="n"/>
       <c r="R461" s="25" t="n"/>
       <c r="S461" s="25" t="n"/>
@@ -75290,11 +74140,7 @@
         <v>1270.04</v>
       </c>
       <c r="O462" s="25" t="n"/>
-      <c r="P462" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P462" s="25" t="n"/>
       <c r="Q462" s="25" t="n"/>
       <c r="R462" s="25" t="n"/>
       <c r="S462" s="25" t="n"/>
@@ -75454,10 +74300,10 @@
         </is>
       </c>
       <c r="Q463" s="25" t="n">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="R463" s="25" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S463" s="25" t="n">
         <v>4474.16</v>
@@ -75618,11 +74464,7 @@
         <v>1216.97</v>
       </c>
       <c r="O464" s="25" t="n"/>
-      <c r="P464" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P464" s="25" t="n"/>
       <c r="Q464" s="25" t="n"/>
       <c r="R464" s="25" t="n"/>
       <c r="S464" s="25" t="n"/>
@@ -75765,7 +74607,9 @@
       <c r="N465" s="25" t="n">
         <v>654.89</v>
       </c>
-      <c r="O465" s="25" t="n"/>
+      <c r="O465" s="25" t="n">
+        <v>1</v>
+      </c>
       <c r="P465" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -75774,17 +74618,9 @@
       <c r="Q465" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="R465" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S465" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="T465" s="25" t="inlineStr">
-        <is>
-          <t>COMPRA B2B</t>
-        </is>
-      </c>
+      <c r="R465" s="25" t="n"/>
+      <c r="S465" s="25" t="n"/>
+      <c r="T465" s="25" t="n"/>
       <c r="U465" s="25" t="n">
         <v>0</v>
       </c>
@@ -75932,11 +74768,7 @@
         <v>1443.35</v>
       </c>
       <c r="O466" s="25" t="n"/>
-      <c r="P466" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P466" s="25" t="n"/>
       <c r="Q466" s="25" t="n"/>
       <c r="R466" s="25" t="n"/>
       <c r="S466" s="25" t="n"/>
@@ -76090,17 +74922,9 @@
       <c r="Q467" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="R467" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S467" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T467" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+      <c r="R467" s="25" t="n"/>
+      <c r="S467" s="25" t="n"/>
+      <c r="T467" s="25" t="n"/>
       <c r="U467" s="25" t="n">
         <v>0</v>
       </c>
@@ -76256,19 +75080,13 @@
         </is>
       </c>
       <c r="Q468" s="25" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="R468" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S468" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T468" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="S468" s="25" t="n"/>
+      <c r="T468" s="25" t="n"/>
       <c r="U468" s="25" t="n">
         <v>0</v>
       </c>
@@ -76428,19 +75246,11 @@
         </is>
       </c>
       <c r="Q469" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R469" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S469" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T469" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="R469" s="25" t="n"/>
+      <c r="S469" s="25" t="n"/>
+      <c r="T469" s="25" t="n"/>
       <c r="U469" s="25" t="n">
         <v>0</v>
       </c>
@@ -76605,7 +75415,7 @@
         </is>
       </c>
       <c r="Q470" s="25" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R470" s="25" t="n">
         <v>3</v>
@@ -76773,10 +75583,10 @@
         </is>
       </c>
       <c r="Q471" s="25" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="R471" s="25" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="S471" s="25" t="n">
         <v>1755.03</v>
@@ -76933,11 +75743,7 @@
         <v>10306.88</v>
       </c>
       <c r="O472" s="25" t="n"/>
-      <c r="P472" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P472" s="25" t="n"/>
       <c r="Q472" s="25" t="n"/>
       <c r="R472" s="25" t="n"/>
       <c r="S472" s="25" t="n"/>
@@ -77077,11 +75883,7 @@
         <v>6881.12</v>
       </c>
       <c r="O473" s="25" t="n"/>
-      <c r="P473" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P473" s="25" t="n"/>
       <c r="Q473" s="25" t="n"/>
       <c r="R473" s="25" t="n"/>
       <c r="S473" s="25" t="n"/>
@@ -77233,7 +76035,7 @@
         </is>
       </c>
       <c r="Q474" s="25" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="R474" s="25" t="n">
         <v>6</v>
@@ -77401,19 +76203,11 @@
         </is>
       </c>
       <c r="Q475" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="R475" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S475" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T475" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="R475" s="25" t="n"/>
+      <c r="S475" s="25" t="n"/>
+      <c r="T475" s="25" t="n"/>
       <c r="U475" s="25" t="n">
         <v>0</v>
       </c>
@@ -77569,19 +76363,11 @@
         </is>
       </c>
       <c r="Q476" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="R476" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S476" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T476" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="R476" s="25" t="n"/>
+      <c r="S476" s="25" t="n"/>
+      <c r="T476" s="25" t="n"/>
       <c r="U476" s="25" t="n">
         <v>0</v>
       </c>
@@ -77737,19 +76523,11 @@
         </is>
       </c>
       <c r="Q477" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="R477" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S477" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T477" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="R477" s="25" t="n"/>
+      <c r="S477" s="25" t="n"/>
+      <c r="T477" s="25" t="n"/>
       <c r="U477" s="25" t="n">
         <v>0</v>
       </c>
@@ -77905,7 +76683,7 @@
         </is>
       </c>
       <c r="Q478" s="25" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="R478" s="25" t="n">
         <v>8</v>
@@ -78073,7 +76851,7 @@
         </is>
       </c>
       <c r="Q479" s="25" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="R479" s="25" t="n">
         <v>9</v>
@@ -78245,19 +77023,13 @@
         </is>
       </c>
       <c r="Q480" s="25" t="n">
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="R480" s="25" t="n">
-        <v>655.95</v>
-      </c>
-      <c r="S480" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T480" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="S480" s="25" t="n"/>
+      <c r="T480" s="25" t="n"/>
       <c r="U480" s="25" t="n">
         <v>0</v>
       </c>
@@ -78409,11 +77181,7 @@
         <v>2969.26</v>
       </c>
       <c r="O481" s="25" t="n"/>
-      <c r="P481" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P481" s="25" t="n"/>
       <c r="Q481" s="25" t="n"/>
       <c r="R481" s="25" t="n"/>
       <c r="S481" s="25" t="n"/>
@@ -78569,11 +77337,7 @@
         <v>2543.68</v>
       </c>
       <c r="O482" s="25" t="n"/>
-      <c r="P482" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P482" s="25" t="n"/>
       <c r="Q482" s="25" t="n"/>
       <c r="R482" s="25" t="n"/>
       <c r="S482" s="25" t="n"/>
@@ -78733,7 +77497,7 @@
         </is>
       </c>
       <c r="Q483" s="25" t="n">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="R483" s="25" t="n">
         <v>39</v>
@@ -78893,19 +77657,13 @@
         </is>
       </c>
       <c r="Q484" s="25" t="n">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="R484" s="25" t="n">
-        <v>451.51</v>
-      </c>
-      <c r="S484" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T484" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="S484" s="25" t="n"/>
+      <c r="T484" s="25" t="n"/>
       <c r="U484" s="25" t="n">
         <v>0</v>
       </c>
@@ -79053,11 +77811,7 @@
         <v>848.4</v>
       </c>
       <c r="O485" s="25" t="n"/>
-      <c r="P485" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P485" s="25" t="n"/>
       <c r="Q485" s="25" t="n"/>
       <c r="R485" s="25" t="n"/>
       <c r="S485" s="25" t="n"/>
@@ -79217,7 +77971,7 @@
         </is>
       </c>
       <c r="Q486" s="25" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="R486" s="25" t="n">
         <v>18</v>
@@ -79377,11 +78131,7 @@
         <v>2421.99</v>
       </c>
       <c r="O487" s="25" t="n"/>
-      <c r="P487" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P487" s="25" t="n"/>
       <c r="Q487" s="25" t="n"/>
       <c r="R487" s="25" t="n"/>
       <c r="S487" s="25" t="n"/>
@@ -79533,11 +78283,7 @@
         <v>1498.5</v>
       </c>
       <c r="O488" s="25" t="n"/>
-      <c r="P488" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P488" s="25" t="n"/>
       <c r="Q488" s="25" t="n"/>
       <c r="R488" s="25" t="n"/>
       <c r="S488" s="25" t="n"/>
@@ -79677,11 +78423,7 @@
         <v>2979.24</v>
       </c>
       <c r="O489" s="25" t="n"/>
-      <c r="P489" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P489" s="25" t="n"/>
       <c r="Q489" s="25" t="n"/>
       <c r="R489" s="25" t="n"/>
       <c r="S489" s="25" t="n"/>
@@ -79821,11 +78563,7 @@
         <v>1033.22</v>
       </c>
       <c r="O490" s="25" t="n"/>
-      <c r="P490" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P490" s="25" t="n"/>
       <c r="Q490" s="25" t="n"/>
       <c r="R490" s="25" t="n"/>
       <c r="S490" s="25" t="n"/>
@@ -79990,19 +78728,11 @@
         </is>
       </c>
       <c r="Q491" s="25" t="n">
-        <v>7</v>
-      </c>
-      <c r="R491" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S491" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T491" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="R491" s="25" t="n"/>
+      <c r="S491" s="25" t="n"/>
+      <c r="T491" s="25" t="n"/>
       <c r="U491" s="25" t="n">
         <v>0</v>
       </c>
@@ -80154,7 +78884,7 @@
         <v>1194.58</v>
       </c>
       <c r="O492" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P492" s="25" t="inlineStr">
         <is>
@@ -80162,19 +78892,13 @@
         </is>
       </c>
       <c r="Q492" s="25" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="R492" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S492" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T492" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="S492" s="25" t="n"/>
+      <c r="T492" s="25" t="n"/>
       <c r="U492" s="25" t="n">
         <v>0</v>
       </c>
@@ -80326,11 +79050,7 @@
         <v>1083.3</v>
       </c>
       <c r="O493" s="25" t="n"/>
-      <c r="P493" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="P493" s="25" t="n"/>
       <c r="Q493" s="25" t="n"/>
       <c r="R493" s="25" t="n"/>
       <c r="S493" s="25" t="n"/>
@@ -80486,11 +79206,7 @@
         <v>1047.3</v>
       </c>
       <c r="O494" s="25" t="n"/>
-      <c r="P494" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P494" s="25" t="n"/>
       <c r="Q494" s="25" t="n"/>
       <c r="R494" s="25" t="n"/>
       <c r="S494" s="25" t="n"/>
@@ -80646,11 +79362,7 @@
         <v>1603.62</v>
       </c>
       <c r="O495" s="25" t="n"/>
-      <c r="P495" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="P495" s="25" t="n"/>
       <c r="Q495" s="25" t="n"/>
       <c r="R495" s="25" t="n"/>
       <c r="S495" s="25" t="n"/>
@@ -80810,10 +79522,10 @@
         </is>
       </c>
       <c r="Q496" s="25" t="n">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="R496" s="25" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S496" s="25" t="n">
         <v>1199</v>
@@ -80968,12 +79680,16 @@
       <c r="O497" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="P497" s="30" t="n"/>
+      <c r="P497" s="30" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="Q497" s="30" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="R497" s="30" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="S497" s="30" t="n">
         <v>2220.81</v>
@@ -81118,12 +79834,16 @@
       <c r="O498" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="P498" s="25" t="n"/>
+      <c r="P498" s="25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="Q498" s="25" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="R498" s="25" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S498" s="25" t="n">
         <v>1333.89</v>
@@ -81276,12 +79996,16 @@
       <c r="O499" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="P499" s="30" t="n"/>
+      <c r="P499" s="30" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="Q499" s="30" t="n">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="R499" s="30" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="S499" s="30" t="n">
         <v>3190.52</v>
@@ -81422,21 +80146,17 @@
       <c r="O500" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="P500" s="25" t="n"/>
+      <c r="P500" s="25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="Q500" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R500" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S500" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T500" s="25" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="R500" s="25" t="n"/>
+      <c r="S500" s="25" t="n"/>
+      <c r="T500" s="25" t="n"/>
       <c r="U500" s="25" t="n">
         <v>0</v>
       </c>
@@ -81544,12 +80264,12 @@
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="F501" t="inlineStr">
+      <c r="F501" s="0" t="inlineStr">
         <is>
           <t>graoemporionatural@gmail.com</t>
         </is>
       </c>
-      <c r="G501" t="inlineStr">
+      <c r="G501" s="0" t="inlineStr">
         <is>
           <t>81309067878195</t>
         </is>
@@ -81578,11 +80298,16 @@
       <c r="O501" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="P501" s="0" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="Q501" s="0" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="R501" s="0" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="S501" s="0" t="n">
         <v>3142.46</v>
@@ -81631,7 +80356,7 @@
       <c r="AH501" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="AI501" t="inlineStr">
+      <c r="AI501" s="0" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -81698,12 +80423,12 @@
           <t>RECIFE</t>
         </is>
       </c>
-      <c r="F502" t="inlineStr">
+      <c r="F502" s="0" t="inlineStr">
         <is>
           <t>graoemporionatural@gmail.com</t>
         </is>
       </c>
-      <c r="G502" t="inlineStr">
+      <c r="G502" s="0" t="inlineStr">
         <is>
           <t>81-9516-7722  LUIZ, 8130120001</t>
         </is>
@@ -81732,11 +80457,16 @@
       <c r="O502" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="P502" s="0" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="Q502" s="0" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="R502" s="0" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S502" s="0" t="n">
         <v>1870.76</v>
@@ -81785,7 +80515,7 @@
       <c r="AH502" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="AI502" t="inlineStr">
+      <c r="AI502" s="0" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -81852,12 +80582,12 @@
           <t>OLINDA</t>
         </is>
       </c>
-      <c r="F503" t="inlineStr">
+      <c r="F503" s="0" t="inlineStr">
         <is>
           <t>graoemporionatural@gmail.com</t>
         </is>
       </c>
-      <c r="G503" t="inlineStr">
+      <c r="G503" s="0" t="inlineStr">
         <is>
           <t>558195167722, 81-9-9516-7722</t>
         </is>
@@ -81884,13 +80614,18 @@
         <v>2020.19</v>
       </c>
       <c r="O503" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="P503" s="0" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
       </c>
       <c r="Q503" s="0" t="n">
-        <v>3</v>
+        <v>142</v>
       </c>
       <c r="R503" s="0" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="S503" s="0" t="n">
         <v>2020.19</v>
@@ -81939,7 +80674,7 @@
       <c r="AH503" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="AI503" t="inlineStr">
+      <c r="AI503" s="0" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -81990,12 +80725,12 @@
           <t>SAPUCAIA</t>
         </is>
       </c>
-      <c r="F504" t="inlineStr">
+      <c r="F504" s="0" t="inlineStr">
         <is>
           <t>emporiomixap@gmail.com</t>
         </is>
       </c>
-      <c r="G504" t="inlineStr">
+      <c r="G504" s="0" t="inlineStr">
         <is>
           <t>+55 (32) 99809-1094</t>
         </is>
@@ -82024,11 +80759,16 @@
       <c r="O504" s="0" t="n">
         <v>13</v>
       </c>
+      <c r="P504" s="0" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="Q504" s="0" t="n">
+        <v>67</v>
+      </c>
+      <c r="R504" s="0" t="n">
         <v>13</v>
-      </c>
-      <c r="R504" s="0" t="n">
-        <v>0</v>
       </c>
       <c r="S504" s="0" t="n">
         <v>1597.24</v>
@@ -82077,7 +80817,7 @@
       <c r="AH504" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="AI504" t="inlineStr">
+      <c r="AI504" s="0" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -82144,12 +80884,12 @@
           <t>BRASILIA</t>
         </is>
       </c>
-      <c r="F505" t="inlineStr">
+      <c r="F505" s="0" t="inlineStr">
         <is>
           <t>cristiane.r.dos.santos@gmail.com</t>
         </is>
       </c>
-      <c r="G505" t="inlineStr">
+      <c r="G505" s="0" t="inlineStr">
         <is>
           <t>+55 (61) 9176-2565</t>
         </is>
@@ -82178,11 +80918,16 @@
       <c r="O505" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="P505" s="0" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="Q505" s="0" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="R505" s="0" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S505" s="0" t="n">
         <v>681.08</v>
@@ -82231,7 +80976,7 @@
       <c r="AH505" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="AI505" t="inlineStr">
+      <c r="AI505" s="0" t="inlineStr">
         <is>
           <t>C</t>
         </is>
